--- a/research/traditional_assets/database/data/poland/poland_trucking.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_trucking.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09099740712084023</v>
+        <v>0.09086096204731064</v>
       </c>
       <c r="C2">
-        <v>2.101750562442028</v>
+        <v>2.083974550772397</v>
       </c>
       <c r="D2">
-        <v>2.101750562442028</v>
+        <v>2.106344550772397</v>
       </c>
       <c r="E2">
-        <v>-1.5</v>
+        <v>-1.47763</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.02237</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1579,28 +1579,28 @@
         <v>0.229</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001125211</v>
       </c>
       <c r="N2">
-        <v>0.229</v>
+        <v>0.227874789</v>
       </c>
       <c r="O2">
-        <v>0.04351</v>
+        <v>0.04329620991</v>
       </c>
       <c r="P2">
-        <v>0.18549</v>
+        <v>0.18457857909</v>
       </c>
       <c r="Q2">
-        <v>0.24449</v>
+        <v>0.24357857909</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09099740712084023</v>
+        <v>0.09136720408819257</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919478</v>
+        <v>0.8345793454163366</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>203.5173847393955</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09086096204731064</v>
+        <v>0.09072451697378105</v>
       </c>
       <c r="C3">
-        <v>2.083974550772397</v>
+        <v>2.066218666096658</v>
       </c>
       <c r="D3">
-        <v>2.106344550772397</v>
+        <v>2.110958666096658</v>
       </c>
       <c r="E3">
-        <v>-1.47763</v>
+        <v>-1.45526</v>
       </c>
       <c r="F3">
-        <v>0.02237</v>
+        <v>0.04474</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1661,28 +1661,28 @@
         <v>0.229</v>
       </c>
       <c r="M3">
-        <v>0.001125211</v>
+        <v>0.002250422</v>
       </c>
       <c r="N3">
-        <v>0.227874789</v>
+        <v>0.226749578</v>
       </c>
       <c r="O3">
-        <v>0.04329620991</v>
+        <v>0.04308241982</v>
       </c>
       <c r="P3">
-        <v>0.18457857909</v>
+        <v>0.18366715818</v>
       </c>
       <c r="Q3">
-        <v>0.24357857909</v>
+        <v>0.24266715818</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09136720408819257</v>
+        <v>0.09174454793242964</v>
       </c>
       <c r="T3">
-        <v>0.8345793454163366</v>
+        <v>0.841490530441223</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>203.5173847393955</v>
+        <v>101.7586923696978</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09072451697378105</v>
+        <v>0.09058807190025145</v>
       </c>
       <c r="C4">
-        <v>2.066218666096658</v>
+        <v>2.04848304097454</v>
       </c>
       <c r="D4">
-        <v>2.110958666096658</v>
+        <v>2.11559304097454</v>
       </c>
       <c r="E4">
-        <v>-1.45526</v>
+        <v>-1.43289</v>
       </c>
       <c r="F4">
-        <v>0.04474</v>
+        <v>0.06711</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1743,28 +1743,28 @@
         <v>0.229</v>
       </c>
       <c r="M4">
-        <v>0.002250422</v>
+        <v>0.003375633</v>
       </c>
       <c r="N4">
-        <v>0.226749578</v>
+        <v>0.225624367</v>
       </c>
       <c r="O4">
-        <v>0.04308241982</v>
+        <v>0.04286862973</v>
       </c>
       <c r="P4">
-        <v>0.18366715818</v>
+        <v>0.18275573727</v>
       </c>
       <c r="Q4">
-        <v>0.24266715818</v>
+        <v>0.24175573727</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09174454793242964</v>
+        <v>0.09212967206211489</v>
       </c>
       <c r="T4">
-        <v>0.841490530441223</v>
+        <v>0.8485442141264163</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>101.7586923696978</v>
+        <v>67.83912824646518</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09058807190025145</v>
+        <v>0.09045162682672185</v>
       </c>
       <c r="C5">
-        <v>2.04848304097454</v>
+        <v>2.03076780913241</v>
       </c>
       <c r="D5">
-        <v>2.11559304097454</v>
+        <v>2.12024780913241</v>
       </c>
       <c r="E5">
-        <v>-1.43289</v>
+        <v>-1.41052</v>
       </c>
       <c r="F5">
-        <v>0.06711</v>
+        <v>0.08948</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1825,28 +1825,28 @@
         <v>0.229</v>
       </c>
       <c r="M5">
-        <v>0.003375633</v>
+        <v>0.004500844</v>
       </c>
       <c r="N5">
-        <v>0.225624367</v>
+        <v>0.224499156</v>
       </c>
       <c r="O5">
-        <v>0.04286862973</v>
+        <v>0.04265483964</v>
       </c>
       <c r="P5">
-        <v>0.18275573727</v>
+        <v>0.18184431636</v>
       </c>
       <c r="Q5">
-        <v>0.24175573727</v>
+        <v>0.24084431636</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09212967206211489</v>
+        <v>0.09252281961116859</v>
       </c>
       <c r="T5">
-        <v>0.8485442141264163</v>
+        <v>0.855744849555051</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.83912824646518</v>
+        <v>50.87934618484888</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09045162682672185</v>
+        <v>0.09031518175319224</v>
       </c>
       <c r="C6">
-        <v>2.03076780913241</v>
+        <v>2.013073105476142</v>
       </c>
       <c r="D6">
-        <v>2.12024780913241</v>
+        <v>2.124923105476142</v>
       </c>
       <c r="E6">
-        <v>-1.41052</v>
+        <v>-1.38815</v>
       </c>
       <c r="F6">
-        <v>0.08948</v>
+        <v>0.11185</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1907,28 +1907,28 @@
         <v>0.229</v>
       </c>
       <c r="M6">
-        <v>0.004500844</v>
+        <v>0.005626055</v>
       </c>
       <c r="N6">
-        <v>0.224499156</v>
+        <v>0.223373945</v>
       </c>
       <c r="O6">
-        <v>0.04265483964</v>
+        <v>0.04244104955</v>
       </c>
       <c r="P6">
-        <v>0.18184431636</v>
+        <v>0.18093289545</v>
       </c>
       <c r="Q6">
-        <v>0.24084431636</v>
+        <v>0.23993289545</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09252281961116859</v>
+        <v>0.09292424395072868</v>
       </c>
       <c r="T6">
-        <v>0.855744849555051</v>
+        <v>0.8630970773084993</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.87934618484888</v>
+        <v>40.70347694787911</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09031518175319224</v>
+        <v>0.09017873667966265</v>
       </c>
       <c r="C7">
-        <v>2.013073105476142</v>
+        <v>1.995399066104146</v>
       </c>
       <c r="D7">
-        <v>2.124923105476142</v>
+        <v>2.129619066104146</v>
       </c>
       <c r="E7">
-        <v>-1.38815</v>
+        <v>-1.36578</v>
       </c>
       <c r="F7">
-        <v>0.11185</v>
+        <v>0.13422</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1989,28 +1989,28 @@
         <v>0.229</v>
       </c>
       <c r="M7">
-        <v>0.005626055</v>
+        <v>0.006751266</v>
       </c>
       <c r="N7">
-        <v>0.223373945</v>
+        <v>0.222248734</v>
       </c>
       <c r="O7">
-        <v>0.04244104955</v>
+        <v>0.04222725945999999</v>
       </c>
       <c r="P7">
-        <v>0.18093289545</v>
+        <v>0.18002147454</v>
       </c>
       <c r="Q7">
-        <v>0.23993289545</v>
+        <v>0.23902147454</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09292424395072868</v>
+        <v>0.09333420923368368</v>
       </c>
       <c r="T7">
-        <v>0.8630970773084993</v>
+        <v>0.8706057354396805</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.70347694787911</v>
+        <v>33.91956412323259</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09017873667966265</v>
+        <v>0.09004229160613306</v>
       </c>
       <c r="C8">
-        <v>1.995399066104146</v>
+        <v>1.977745828320578</v>
       </c>
       <c r="D8">
-        <v>2.129619066104146</v>
+        <v>2.134335828320578</v>
       </c>
       <c r="E8">
-        <v>-1.36578</v>
+        <v>-1.34341</v>
       </c>
       <c r="F8">
-        <v>0.13422</v>
+        <v>0.15659</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2071,28 +2071,28 @@
         <v>0.229</v>
       </c>
       <c r="M8">
-        <v>0.006751266</v>
+        <v>0.007876476999999998</v>
       </c>
       <c r="N8">
-        <v>0.222248734</v>
+        <v>0.221123523</v>
       </c>
       <c r="O8">
-        <v>0.04222725945999999</v>
+        <v>0.04201346937</v>
       </c>
       <c r="P8">
-        <v>0.18002147454</v>
+        <v>0.17911005363</v>
       </c>
       <c r="Q8">
-        <v>0.23902147454</v>
+        <v>0.23811005363</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09333420923368368</v>
+        <v>0.09375299097433662</v>
       </c>
       <c r="T8">
-        <v>0.8706057354396805</v>
+        <v>0.8782758700898118</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.91956412323259</v>
+        <v>29.07391210562794</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09004229160613306</v>
+        <v>0.08990584653260346</v>
       </c>
       <c r="C9">
-        <v>1.977745828320578</v>
+        <v>1.960113530648718</v>
       </c>
       <c r="D9">
-        <v>2.134335828320578</v>
+        <v>2.139073530648718</v>
       </c>
       <c r="E9">
-        <v>-1.34341</v>
+        <v>-1.32104</v>
       </c>
       <c r="F9">
-        <v>0.15659</v>
+        <v>0.17896</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2153,28 +2153,28 @@
         <v>0.229</v>
       </c>
       <c r="M9">
-        <v>0.007876477000000002</v>
+        <v>0.009001688000000001</v>
       </c>
       <c r="N9">
-        <v>0.221123523</v>
+        <v>0.219998312</v>
       </c>
       <c r="O9">
-        <v>0.04201346937</v>
+        <v>0.04179967927999999</v>
       </c>
       <c r="P9">
-        <v>0.17911005363</v>
+        <v>0.17819863272</v>
       </c>
       <c r="Q9">
-        <v>0.23811005363</v>
+        <v>0.23719863272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09375299097433662</v>
+        <v>0.09418087666587333</v>
       </c>
       <c r="T9">
-        <v>0.8782758700898118</v>
+        <v>0.8861127467975547</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.07391210562793</v>
+        <v>25.43967309242444</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08990584653260346</v>
+        <v>0.08976940145907386</v>
       </c>
       <c r="C10">
-        <v>1.960113530648718</v>
+        <v>1.942502312844534</v>
       </c>
       <c r="D10">
-        <v>2.139073530648718</v>
+        <v>2.143832312844534</v>
       </c>
       <c r="E10">
-        <v>-1.32104</v>
+        <v>-1.29867</v>
       </c>
       <c r="F10">
-        <v>0.17896</v>
+        <v>0.20133</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2235,28 +2235,28 @@
         <v>0.229</v>
       </c>
       <c r="M10">
-        <v>0.009001688000000001</v>
+        <v>0.010126899</v>
       </c>
       <c r="N10">
-        <v>0.219998312</v>
+        <v>0.218873101</v>
       </c>
       <c r="O10">
-        <v>0.04179967927999999</v>
+        <v>0.04158588919</v>
       </c>
       <c r="P10">
-        <v>0.17819863272</v>
+        <v>0.17728721181</v>
       </c>
       <c r="Q10">
-        <v>0.23719863272</v>
+        <v>0.23628721181</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09418087666587333</v>
+        <v>0.09461816643854271</v>
       </c>
       <c r="T10">
-        <v>0.8861127467975547</v>
+        <v>0.8941218625538192</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.43967309242444</v>
+        <v>22.61304274882173</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08976940145907386</v>
+        <v>0.08963295638554428</v>
       </c>
       <c r="C11">
-        <v>1.942502312844534</v>
+        <v>1.924912315910424</v>
       </c>
       <c r="D11">
-        <v>2.143832312844534</v>
+        <v>2.148612315910424</v>
       </c>
       <c r="E11">
-        <v>-1.29867</v>
+        <v>-1.2763</v>
       </c>
       <c r="F11">
-        <v>0.20133</v>
+        <v>0.2237</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2317,28 +2317,28 @@
         <v>0.229</v>
       </c>
       <c r="M11">
-        <v>0.010126899</v>
+        <v>0.01125211</v>
       </c>
       <c r="N11">
-        <v>0.218873101</v>
+        <v>0.21774789</v>
       </c>
       <c r="O11">
-        <v>0.04158588919</v>
+        <v>0.0413720991</v>
       </c>
       <c r="P11">
-        <v>0.17728721181</v>
+        <v>0.1763757909</v>
       </c>
       <c r="Q11">
-        <v>0.23628721181</v>
+        <v>0.2353757909</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09461816643854271</v>
+        <v>0.09506517376171586</v>
       </c>
       <c r="T11">
-        <v>0.8941218625538192</v>
+        <v>0.9023089586602232</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.61304274882173</v>
+        <v>20.35173847393955</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08963295638554428</v>
+        <v>0.08949651131201468</v>
       </c>
       <c r="C12">
-        <v>1.924912315910424</v>
+        <v>1.907343682109143</v>
       </c>
       <c r="D12">
-        <v>2.148612315910424</v>
+        <v>2.153413682109143</v>
       </c>
       <c r="E12">
-        <v>-1.2763</v>
+        <v>-1.25393</v>
       </c>
       <c r="F12">
-        <v>0.2237</v>
+        <v>0.24607</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2399,28 +2399,28 @@
         <v>0.229</v>
       </c>
       <c r="M12">
-        <v>0.01125211</v>
+        <v>0.012377321</v>
       </c>
       <c r="N12">
-        <v>0.21774789</v>
+        <v>0.216622679</v>
       </c>
       <c r="O12">
-        <v>0.0413720991</v>
+        <v>0.04115830901</v>
       </c>
       <c r="P12">
-        <v>0.1763757909</v>
+        <v>0.17546436999</v>
       </c>
       <c r="Q12">
-        <v>0.2353757909</v>
+        <v>0.23446436999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09506517376171586</v>
+        <v>0.09552222619327491</v>
       </c>
       <c r="T12">
-        <v>0.9023089586602232</v>
+        <v>0.9106800344544114</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.35173847393955</v>
+        <v>18.50158043085414</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08949651131201468</v>
+        <v>0.08936006623848508</v>
       </c>
       <c r="C13">
-        <v>1.907343682109143</v>
+        <v>1.889796554977913</v>
       </c>
       <c r="D13">
-        <v>2.153413682109143</v>
+        <v>2.158236554977913</v>
       </c>
       <c r="E13">
-        <v>-1.25393</v>
+        <v>-1.23156</v>
       </c>
       <c r="F13">
-        <v>0.24607</v>
+        <v>0.26844</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2481,28 +2481,28 @@
         <v>0.229</v>
       </c>
       <c r="M13">
-        <v>0.012377321</v>
+        <v>0.013502532</v>
       </c>
       <c r="N13">
-        <v>0.216622679</v>
+        <v>0.215497468</v>
       </c>
       <c r="O13">
-        <v>0.04115830901</v>
+        <v>0.04094451891999999</v>
       </c>
       <c r="P13">
-        <v>0.17546436999</v>
+        <v>0.17455294908</v>
       </c>
       <c r="Q13">
-        <v>0.23446436999</v>
+        <v>0.23355294908</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09552222619327491</v>
+        <v>0.09598966618009667</v>
       </c>
       <c r="T13">
-        <v>0.9106800344544114</v>
+        <v>0.9192413619711948</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.50158043085414</v>
+        <v>16.95978206161629</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08936006623848508</v>
+        <v>0.08922362116495548</v>
       </c>
       <c r="C14">
-        <v>1.889796554977913</v>
+        <v>1.872271079342733</v>
       </c>
       <c r="D14">
-        <v>2.158236554977913</v>
+        <v>2.163081079342733</v>
       </c>
       <c r="E14">
-        <v>-1.23156</v>
+        <v>-1.20919</v>
       </c>
       <c r="F14">
-        <v>0.26844</v>
+        <v>0.29081</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2563,28 +2563,28 @@
         <v>0.229</v>
       </c>
       <c r="M14">
-        <v>0.013502532</v>
+        <v>0.014627743</v>
       </c>
       <c r="N14">
-        <v>0.215497468</v>
+        <v>0.214372257</v>
       </c>
       <c r="O14">
-        <v>0.04094451891999999</v>
+        <v>0.04073072883</v>
       </c>
       <c r="P14">
-        <v>0.17455294908</v>
+        <v>0.17364152817</v>
       </c>
       <c r="Q14">
-        <v>0.23355294908</v>
+        <v>0.23264152817</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09598966618009667</v>
+        <v>0.09646785191374194</v>
       </c>
       <c r="T14">
-        <v>0.9192413619711948</v>
+        <v>0.9279995016148008</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.95978206161629</v>
+        <v>15.65518344149196</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08922362116495548</v>
+        <v>0.08908717609142588</v>
       </c>
       <c r="C15">
-        <v>1.872271079342733</v>
+        <v>1.854767401332868</v>
       </c>
       <c r="D15">
-        <v>2.163081079342733</v>
+        <v>2.167947401332868</v>
       </c>
       <c r="E15">
-        <v>-1.20919</v>
+        <v>-1.18682</v>
       </c>
       <c r="F15">
-        <v>0.29081</v>
+        <v>0.3131800000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2645,28 +2645,28 @@
         <v>0.229</v>
       </c>
       <c r="M15">
-        <v>0.014627743</v>
+        <v>0.015752954</v>
       </c>
       <c r="N15">
-        <v>0.214372257</v>
+        <v>0.213247046</v>
       </c>
       <c r="O15">
-        <v>0.04073072883</v>
+        <v>0.04051693873999999</v>
       </c>
       <c r="P15">
-        <v>0.17364152817</v>
+        <v>0.17273010726</v>
       </c>
       <c r="Q15">
-        <v>0.23264152817</v>
+        <v>0.23173010726</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09646785191374194</v>
+        <v>0.09695715824584406</v>
       </c>
       <c r="T15">
-        <v>0.9279995016148008</v>
+        <v>0.9369613189245373</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.65518344149196</v>
+        <v>14.53695605281396</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08908717609142588</v>
+        <v>0.0889507310178963</v>
       </c>
       <c r="C16">
-        <v>1.854767401332868</v>
+        <v>1.837285668395551</v>
       </c>
       <c r="D16">
-        <v>2.167947401332868</v>
+        <v>2.172835668395551</v>
       </c>
       <c r="E16">
-        <v>-1.18682</v>
+        <v>-1.16445</v>
       </c>
       <c r="F16">
-        <v>0.3131800000000001</v>
+        <v>0.3355500000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2727,28 +2727,28 @@
         <v>0.229</v>
       </c>
       <c r="M16">
-        <v>0.015752954</v>
+        <v>0.016878165</v>
       </c>
       <c r="N16">
-        <v>0.213247046</v>
+        <v>0.212121835</v>
       </c>
       <c r="O16">
-        <v>0.04051693873999999</v>
+        <v>0.04030314865</v>
       </c>
       <c r="P16">
-        <v>0.17273010726</v>
+        <v>0.17181868635</v>
       </c>
       <c r="Q16">
-        <v>0.23173010726</v>
+        <v>0.23081868635</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09695715824584406</v>
+        <v>0.09745797766811329</v>
       </c>
       <c r="T16">
-        <v>0.9369613189245373</v>
+        <v>0.9461340025239146</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.53695605281396</v>
+        <v>13.56782564929303</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0889507310178963</v>
+        <v>0.0890086859443667</v>
       </c>
       <c r="C17">
-        <v>1.837285668395551</v>
+        <v>1.812836690693061</v>
       </c>
       <c r="D17">
-        <v>2.172835668395551</v>
+        <v>2.170756690693061</v>
       </c>
       <c r="E17">
-        <v>-1.16445</v>
+        <v>-1.14208</v>
       </c>
       <c r="F17">
-        <v>0.33555</v>
+        <v>0.35792</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2809,45 +2809,45 @@
         <v>0.229</v>
       </c>
       <c r="M17">
-        <v>0.016878165</v>
+        <v>0.018540256</v>
       </c>
       <c r="N17">
-        <v>0.212121835</v>
+        <v>0.210459744</v>
       </c>
       <c r="O17">
-        <v>0.04030314865</v>
+        <v>0.03998735136</v>
       </c>
       <c r="P17">
-        <v>0.17181868635</v>
+        <v>0.17047239264</v>
       </c>
       <c r="Q17">
-        <v>0.23081868635</v>
+        <v>0.22947239264</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09745797766811329</v>
+        <v>0.09797072136234131</v>
       </c>
       <c r="T17">
-        <v>0.9461340025239146</v>
+        <v>0.9555250833518484</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.19</v>
       </c>
       <c r="W17">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.56782564929303</v>
+        <v>12.35150151109024</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0890086859443667</v>
+        <v>0.08888439087083709</v>
       </c>
       <c r="C18">
-        <v>1.812836690693061</v>
+        <v>1.79493033686206</v>
       </c>
       <c r="D18">
-        <v>2.170756690693061</v>
+        <v>2.17522033686206</v>
       </c>
       <c r="E18">
-        <v>-1.14208</v>
+        <v>-1.11971</v>
       </c>
       <c r="F18">
-        <v>0.35792</v>
+        <v>0.38029</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2891,28 +2891,28 @@
         <v>0.229</v>
       </c>
       <c r="M18">
-        <v>0.018540256</v>
+        <v>0.019699022</v>
       </c>
       <c r="N18">
-        <v>0.210459744</v>
+        <v>0.209300978</v>
       </c>
       <c r="O18">
-        <v>0.03998735136</v>
+        <v>0.03976718582</v>
       </c>
       <c r="P18">
-        <v>0.17047239264</v>
+        <v>0.16953379218</v>
       </c>
       <c r="Q18">
-        <v>0.22947239264</v>
+        <v>0.22853379218</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09797072136234131</v>
+        <v>0.09849582032630975</v>
       </c>
       <c r="T18">
-        <v>0.9555250833518484</v>
+        <v>0.9651424552840698</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.35150151109024</v>
+        <v>11.62494259867317</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08888439087083709</v>
+        <v>0.08876009579730749</v>
       </c>
       <c r="C19">
-        <v>1.79493033686206</v>
+        <v>1.777042377714245</v>
       </c>
       <c r="D19">
-        <v>2.17522033686206</v>
+        <v>2.179702377714245</v>
       </c>
       <c r="E19">
-        <v>-1.11971</v>
+        <v>-1.09734</v>
       </c>
       <c r="F19">
-        <v>0.38029</v>
+        <v>0.4026600000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2973,28 +2973,28 @@
         <v>0.229</v>
       </c>
       <c r="M19">
-        <v>0.019699022</v>
+        <v>0.020857788</v>
       </c>
       <c r="N19">
-        <v>0.209300978</v>
+        <v>0.208142212</v>
       </c>
       <c r="O19">
-        <v>0.03976718582</v>
+        <v>0.03954702028</v>
       </c>
       <c r="P19">
-        <v>0.16953379218</v>
+        <v>0.16859519172</v>
       </c>
       <c r="Q19">
-        <v>0.22853379218</v>
+        <v>0.22759519172</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09849582032630975</v>
+        <v>0.09903372658208232</v>
       </c>
       <c r="T19">
-        <v>0.9651424552840698</v>
+        <v>0.9749943972634185</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.62494259867317</v>
+        <v>10.97911245430244</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08876009579730751</v>
+        <v>0.08863580072377791</v>
       </c>
       <c r="C20">
-        <v>1.777042377714245</v>
+        <v>1.759172927191111</v>
       </c>
       <c r="D20">
-        <v>2.179702377714245</v>
+        <v>2.184202927191111</v>
       </c>
       <c r="E20">
-        <v>-1.09734</v>
+        <v>-1.07497</v>
       </c>
       <c r="F20">
-        <v>0.40266</v>
+        <v>0.42503</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3055,28 +3055,28 @@
         <v>0.229</v>
       </c>
       <c r="M20">
-        <v>0.020857788</v>
+        <v>0.022016554</v>
       </c>
       <c r="N20">
-        <v>0.208142212</v>
+        <v>0.206983446</v>
       </c>
       <c r="O20">
-        <v>0.03954702028</v>
+        <v>0.03932685474</v>
       </c>
       <c r="P20">
-        <v>0.16859519172</v>
+        <v>0.16765659126</v>
       </c>
       <c r="Q20">
-        <v>0.22759519172</v>
+        <v>0.22665659126</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09903372658208232</v>
+        <v>0.09958491447379988</v>
       </c>
       <c r="T20">
-        <v>0.9749943972634185</v>
+        <v>0.9850895970694179</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.97911245430244</v>
+        <v>10.40126443039179</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08863580072377791</v>
+        <v>0.08851150565024832</v>
       </c>
       <c r="C21">
-        <v>1.759172927191111</v>
+        <v>1.741322100177144</v>
       </c>
       <c r="D21">
-        <v>2.184202927191111</v>
+        <v>2.188722100177144</v>
       </c>
       <c r="E21">
-        <v>-1.07497</v>
+        <v>-1.0526</v>
       </c>
       <c r="F21">
-        <v>0.42503</v>
+        <v>0.4474</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3137,28 +3137,28 @@
         <v>0.229</v>
       </c>
       <c r="M21">
-        <v>0.022016554</v>
+        <v>0.02317532</v>
       </c>
       <c r="N21">
-        <v>0.206983446</v>
+        <v>0.20582468</v>
       </c>
       <c r="O21">
-        <v>0.03932685474</v>
+        <v>0.0391066892</v>
       </c>
       <c r="P21">
-        <v>0.16765659126</v>
+        <v>0.1667179908</v>
       </c>
       <c r="Q21">
-        <v>0.22665659126</v>
+        <v>0.2257179908</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09958491447379988</v>
+        <v>0.1001498820628104</v>
       </c>
       <c r="T21">
-        <v>0.9850895970694179</v>
+        <v>0.9954371768705674</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.40126443039179</v>
+        <v>9.881201208872197</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08851150565024832</v>
+        <v>0.08867638057671873</v>
       </c>
       <c r="C22">
-        <v>1.741322100177144</v>
+        <v>1.712961545929437</v>
       </c>
       <c r="D22">
-        <v>2.188722100177144</v>
+        <v>2.182731545929437</v>
       </c>
       <c r="E22">
-        <v>-1.0526</v>
+        <v>-1.03023</v>
       </c>
       <c r="F22">
-        <v>0.4474</v>
+        <v>0.4697700000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3219,45 +3219,45 @@
         <v>0.229</v>
       </c>
       <c r="M22">
-        <v>0.02317532</v>
+        <v>0.025132695</v>
       </c>
       <c r="N22">
-        <v>0.20582468</v>
+        <v>0.203867305</v>
       </c>
       <c r="O22">
-        <v>0.0391066892</v>
+        <v>0.03873478795</v>
       </c>
       <c r="P22">
-        <v>0.1667179908</v>
+        <v>0.16513251705</v>
       </c>
       <c r="Q22">
-        <v>0.2257179908</v>
+        <v>0.22413251705</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1001498820628104</v>
+        <v>0.1007291526287579</v>
       </c>
       <c r="T22">
-        <v>0.9954371768705674</v>
+        <v>1.006046720717315</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.19</v>
       </c>
       <c r="W22">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.881201208872197</v>
+        <v>9.111637251794921</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08867638057671873</v>
+        <v>0.08856585550318913</v>
       </c>
       <c r="C23">
-        <v>1.712961545929437</v>
+        <v>1.694603726486837</v>
       </c>
       <c r="D23">
-        <v>2.182731545929437</v>
+        <v>2.186743726486837</v>
       </c>
       <c r="E23">
-        <v>-1.03023</v>
+        <v>-1.00786</v>
       </c>
       <c r="F23">
-        <v>0.46977</v>
+        <v>0.49214</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3301,28 +3301,28 @@
         <v>0.229</v>
       </c>
       <c r="M23">
-        <v>0.025132695</v>
+        <v>0.02632949</v>
       </c>
       <c r="N23">
-        <v>0.203867305</v>
+        <v>0.20267051</v>
       </c>
       <c r="O23">
-        <v>0.03873478795</v>
+        <v>0.0385073969</v>
       </c>
       <c r="P23">
-        <v>0.16513251705</v>
+        <v>0.1641631131</v>
       </c>
       <c r="Q23">
-        <v>0.22413251705</v>
+        <v>0.2231631131</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1007291526287579</v>
+        <v>0.1013232762861399</v>
       </c>
       <c r="T23">
-        <v>1.006046720717315</v>
+        <v>1.016928304149878</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.111637251794921</v>
+        <v>8.69747192216788</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08856585550318913</v>
+        <v>0.08845533042965953</v>
       </c>
       <c r="C24">
-        <v>1.694603726486837</v>
+        <v>1.676260684158795</v>
       </c>
       <c r="D24">
-        <v>2.186743726486837</v>
+        <v>2.190770684158795</v>
       </c>
       <c r="E24">
-        <v>-1.00786</v>
+        <v>-0.98549</v>
       </c>
       <c r="F24">
-        <v>0.49214</v>
+        <v>0.51451</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3383,28 +3383,28 @@
         <v>0.229</v>
       </c>
       <c r="M24">
-        <v>0.02632949</v>
+        <v>0.027526285</v>
       </c>
       <c r="N24">
-        <v>0.20267051</v>
+        <v>0.201473715</v>
       </c>
       <c r="O24">
-        <v>0.0385073969</v>
+        <v>0.03828000584999999</v>
       </c>
       <c r="P24">
-        <v>0.1641631131</v>
+        <v>0.16319370915</v>
       </c>
       <c r="Q24">
-        <v>0.2231631131</v>
+        <v>0.22219370915</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1013232762861399</v>
+        <v>0.1019328317268305</v>
       </c>
       <c r="T24">
-        <v>1.016928304149878</v>
+        <v>1.028092526113155</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.69747192216788</v>
+        <v>8.319320969030144</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08845533042965953</v>
+        <v>0.08834480535612993</v>
       </c>
       <c r="C25">
-        <v>1.676260684158795</v>
+        <v>1.657932500733496</v>
       </c>
       <c r="D25">
-        <v>2.190770684158795</v>
+        <v>2.194812500733496</v>
       </c>
       <c r="E25">
-        <v>-0.98549</v>
+        <v>-0.96312</v>
       </c>
       <c r="F25">
-        <v>0.51451</v>
+        <v>0.53688</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3465,28 +3465,28 @@
         <v>0.229</v>
       </c>
       <c r="M25">
-        <v>0.027526285</v>
+        <v>0.02872308</v>
       </c>
       <c r="N25">
-        <v>0.201473715</v>
+        <v>0.20027692</v>
       </c>
       <c r="O25">
-        <v>0.03828000584999999</v>
+        <v>0.0380526148</v>
       </c>
       <c r="P25">
-        <v>0.16319370915</v>
+        <v>0.1622243052</v>
       </c>
       <c r="Q25">
-        <v>0.22219370915</v>
+        <v>0.2212243052</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1019328317268305</v>
+        <v>0.1025584281001709</v>
       </c>
       <c r="T25">
-        <v>1.028092526113155</v>
+        <v>1.039550543391257</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.319320969030144</v>
+        <v>7.972682595320556</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08834480535612993</v>
+        <v>0.08823428028260033</v>
       </c>
       <c r="C26">
-        <v>1.657932500733496</v>
+        <v>1.639619258603814</v>
       </c>
       <c r="D26">
-        <v>2.194812500733496</v>
+        <v>2.198869258603814</v>
       </c>
       <c r="E26">
-        <v>-0.96312</v>
+        <v>-0.94075</v>
       </c>
       <c r="F26">
-        <v>0.53688</v>
+        <v>0.55925</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3547,28 +3547,28 @@
         <v>0.229</v>
       </c>
       <c r="M26">
-        <v>0.02872308</v>
+        <v>0.029919875</v>
       </c>
       <c r="N26">
-        <v>0.20027692</v>
+        <v>0.199080125</v>
       </c>
       <c r="O26">
-        <v>0.0380526148</v>
+        <v>0.03782522375</v>
       </c>
       <c r="P26">
-        <v>0.1622243052</v>
+        <v>0.16125490125</v>
       </c>
       <c r="Q26">
-        <v>0.2212243052</v>
+        <v>0.22025490125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1025584281001709</v>
+        <v>0.1032007070434671</v>
       </c>
       <c r="T26">
-        <v>1.039550543391257</v>
+        <v>1.051314107796774</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.972682595320556</v>
+        <v>7.653775291507734</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08823428028260033</v>
+        <v>0.08829223520907074</v>
       </c>
       <c r="C27">
-        <v>1.639619258603814</v>
+        <v>1.615120188780973</v>
       </c>
       <c r="D27">
-        <v>2.198869258603814</v>
+        <v>2.196740188780973</v>
       </c>
       <c r="E27">
-        <v>-0.94075</v>
+        <v>-0.91838</v>
       </c>
       <c r="F27">
-        <v>0.55925</v>
+        <v>0.58162</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3629,45 +3629,45 @@
         <v>0.229</v>
       </c>
       <c r="M27">
-        <v>0.029919875</v>
+        <v>0.031581966</v>
       </c>
       <c r="N27">
-        <v>0.199080125</v>
+        <v>0.197418034</v>
       </c>
       <c r="O27">
-        <v>0.03782522375</v>
+        <v>0.03750942645999999</v>
       </c>
       <c r="P27">
-        <v>0.16125490125</v>
+        <v>0.15990860754</v>
       </c>
       <c r="Q27">
-        <v>0.22025490125</v>
+        <v>0.21890860754</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1032007070434671</v>
+        <v>0.1038603448771226</v>
       </c>
       <c r="T27">
-        <v>1.051314107796774</v>
+        <v>1.063395606375413</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.19</v>
       </c>
       <c r="W27">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.653775291507734</v>
+        <v>7.250973546105393</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08829223520907074</v>
+        <v>0.08818819013554112</v>
       </c>
       <c r="C28">
-        <v>1.615120188780973</v>
+        <v>1.596575404573249</v>
       </c>
       <c r="D28">
-        <v>2.196740188780973</v>
+        <v>2.200565404573249</v>
       </c>
       <c r="E28">
-        <v>-0.91838</v>
+        <v>-0.89601</v>
       </c>
       <c r="F28">
-        <v>0.58162</v>
+        <v>0.60399</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3711,28 +3711,28 @@
         <v>0.229</v>
       </c>
       <c r="M28">
-        <v>0.031581966</v>
+        <v>0.032796657</v>
       </c>
       <c r="N28">
-        <v>0.197418034</v>
+        <v>0.196203343</v>
       </c>
       <c r="O28">
-        <v>0.03750942645999999</v>
+        <v>0.03727863517</v>
       </c>
       <c r="P28">
-        <v>0.15990860754</v>
+        <v>0.15892470783</v>
       </c>
       <c r="Q28">
-        <v>0.21890860754</v>
+        <v>0.21792470783</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1038603448771226</v>
+        <v>0.1045380549801933</v>
       </c>
       <c r="T28">
-        <v>1.063395606375413</v>
+        <v>1.075808104915111</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.250973546105393</v>
+        <v>6.982418970323712</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08818819013554112</v>
+        <v>0.08808414506201152</v>
       </c>
       <c r="C29">
-        <v>1.596575404573249</v>
+        <v>1.578043965411765</v>
       </c>
       <c r="D29">
-        <v>2.200565404573249</v>
+        <v>2.204403965411765</v>
       </c>
       <c r="E29">
-        <v>-0.89601</v>
+        <v>-0.8736399999999999</v>
       </c>
       <c r="F29">
-        <v>0.60399</v>
+        <v>0.6263600000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3793,28 +3793,28 @@
         <v>0.229</v>
       </c>
       <c r="M29">
-        <v>0.032796657</v>
+        <v>0.03401134800000001</v>
       </c>
       <c r="N29">
-        <v>0.196203343</v>
+        <v>0.194988652</v>
       </c>
       <c r="O29">
-        <v>0.03727863517</v>
+        <v>0.03704784388</v>
       </c>
       <c r="P29">
-        <v>0.15892470783</v>
+        <v>0.15794080812</v>
       </c>
       <c r="Q29">
-        <v>0.21792470783</v>
+        <v>0.21694080812</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1045380549801933</v>
+        <v>0.1052345903639049</v>
       </c>
       <c r="T29">
-        <v>1.075808104915111</v>
+        <v>1.088565395080911</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.982418970323712</v>
+        <v>6.733046864240722</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08808414506201152</v>
+        <v>0.08798009998848194</v>
       </c>
       <c r="C30">
-        <v>1.578043965411765</v>
+        <v>1.559525941253928</v>
       </c>
       <c r="D30">
-        <v>2.204403965411765</v>
+        <v>2.208255941253928</v>
       </c>
       <c r="E30">
-        <v>-0.8736399999999999</v>
+        <v>-0.8512699999999999</v>
       </c>
       <c r="F30">
-        <v>0.6263600000000001</v>
+        <v>0.6487300000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3875,28 +3875,28 @@
         <v>0.229</v>
       </c>
       <c r="M30">
-        <v>0.03401134800000001</v>
+        <v>0.03522603900000001</v>
       </c>
       <c r="N30">
-        <v>0.194988652</v>
+        <v>0.193773961</v>
       </c>
       <c r="O30">
-        <v>0.03704784388</v>
+        <v>0.03681705259</v>
       </c>
       <c r="P30">
-        <v>0.15794080812</v>
+        <v>0.15695690841</v>
       </c>
       <c r="Q30">
-        <v>0.21694080812</v>
+        <v>0.21595690841</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1052345903639049</v>
+        <v>0.1059507464626506</v>
       </c>
       <c r="T30">
-        <v>1.088565395080911</v>
+        <v>1.101682045533073</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.733046864240722</v>
+        <v>6.500872834439317</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08798009998848194</v>
+        <v>0.08787605491495233</v>
       </c>
       <c r="C31">
-        <v>1.559525941253928</v>
+        <v>1.541021402546979</v>
       </c>
       <c r="D31">
-        <v>2.208255941253928</v>
+        <v>2.212121402546979</v>
       </c>
       <c r="E31">
-        <v>-0.85127</v>
+        <v>-0.8289</v>
       </c>
       <c r="F31">
-        <v>0.64873</v>
+        <v>0.6711</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3957,28 +3957,28 @@
         <v>0.229</v>
       </c>
       <c r="M31">
-        <v>0.035226039</v>
+        <v>0.03644073</v>
       </c>
       <c r="N31">
-        <v>0.193773961</v>
+        <v>0.19255927</v>
       </c>
       <c r="O31">
-        <v>0.03681705259</v>
+        <v>0.0365862613</v>
       </c>
       <c r="P31">
-        <v>0.15695690841</v>
+        <v>0.1559730087</v>
       </c>
       <c r="Q31">
-        <v>0.21595690841</v>
+        <v>0.2149730087</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1059507464626506</v>
+        <v>0.1066873641642176</v>
       </c>
       <c r="T31">
-        <v>1.101682045533072</v>
+        <v>1.115173457426724</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.500872834439319</v>
+        <v>6.284177073291341</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08787605491495233</v>
+        <v>0.08802310984142274</v>
       </c>
       <c r="C32">
-        <v>1.541021402546979</v>
+        <v>1.513191991518624</v>
       </c>
       <c r="D32">
-        <v>2.212121402546979</v>
+        <v>2.206661991518624</v>
       </c>
       <c r="E32">
-        <v>-0.8289</v>
+        <v>-0.80653</v>
       </c>
       <c r="F32">
-        <v>0.6711</v>
+        <v>0.69347</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4039,45 +4039,45 @@
         <v>0.229</v>
       </c>
       <c r="M32">
-        <v>0.03644073</v>
+        <v>0.038348891</v>
       </c>
       <c r="N32">
-        <v>0.19255927</v>
+        <v>0.190651109</v>
       </c>
       <c r="O32">
-        <v>0.0365862613</v>
+        <v>0.03622371071</v>
       </c>
       <c r="P32">
-        <v>0.1559730087</v>
+        <v>0.15442739829</v>
       </c>
       <c r="Q32">
-        <v>0.2149730087</v>
+        <v>0.21342739829</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1066873641642176</v>
+        <v>0.1074453331035112</v>
       </c>
       <c r="T32">
-        <v>1.115173457426724</v>
+        <v>1.129055924737583</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.19</v>
       </c>
       <c r="W32">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.284177073291341</v>
+        <v>5.971489501482584</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08802310984142274</v>
+        <v>0.08792716476789315</v>
       </c>
       <c r="C33">
-        <v>1.513191991518624</v>
+        <v>1.49438089013394</v>
       </c>
       <c r="D33">
-        <v>2.206661991518624</v>
+        <v>2.21022089013394</v>
       </c>
       <c r="E33">
-        <v>-0.80653</v>
+        <v>-0.78416</v>
       </c>
       <c r="F33">
-        <v>0.69347</v>
+        <v>0.71584</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4121,28 +4121,28 @@
         <v>0.229</v>
       </c>
       <c r="M33">
-        <v>0.038348891</v>
+        <v>0.039585952</v>
       </c>
       <c r="N33">
-        <v>0.190651109</v>
+        <v>0.189414048</v>
       </c>
       <c r="O33">
-        <v>0.03622371071</v>
+        <v>0.03598866912</v>
       </c>
       <c r="P33">
-        <v>0.15442739829</v>
+        <v>0.15342537888</v>
       </c>
       <c r="Q33">
-        <v>0.21342739829</v>
+        <v>0.21242537888</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1074453331035112</v>
+        <v>0.1082255952469017</v>
       </c>
       <c r="T33">
-        <v>1.129055924737583</v>
+        <v>1.143346699910526</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.971489501482584</v>
+        <v>5.784880454561254</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08792716476789315</v>
+        <v>0.08783121969436354</v>
       </c>
       <c r="C34">
-        <v>1.49438089013394</v>
+        <v>1.475581286857898</v>
       </c>
       <c r="D34">
-        <v>2.21022089013394</v>
+        <v>2.213791286857898</v>
       </c>
       <c r="E34">
-        <v>-0.78416</v>
+        <v>-0.76179</v>
       </c>
       <c r="F34">
-        <v>0.71584</v>
+        <v>0.73821</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4203,28 +4203,28 @@
         <v>0.229</v>
       </c>
       <c r="M34">
-        <v>0.039585952</v>
+        <v>0.04082301300000001</v>
       </c>
       <c r="N34">
-        <v>0.189414048</v>
+        <v>0.188176987</v>
       </c>
       <c r="O34">
-        <v>0.03598866912</v>
+        <v>0.03575362752999999</v>
       </c>
       <c r="P34">
-        <v>0.15342537888</v>
+        <v>0.15242335947</v>
       </c>
       <c r="Q34">
-        <v>0.21242537888</v>
+        <v>0.21142335947</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1082255952469017</v>
+        <v>0.1090291487975575</v>
       </c>
       <c r="T34">
-        <v>1.143346699910526</v>
+        <v>1.158064065387139</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.784880454561254</v>
+        <v>5.609581046847276</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08783121969436354</v>
+        <v>0.08773527462083396</v>
       </c>
       <c r="C35">
-        <v>1.475581286857898</v>
+        <v>1.45679323750288</v>
       </c>
       <c r="D35">
-        <v>2.213791286857898</v>
+        <v>2.21737323750288</v>
       </c>
       <c r="E35">
-        <v>-0.76179</v>
+        <v>-0.73942</v>
       </c>
       <c r="F35">
-        <v>0.73821</v>
+        <v>0.76058</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4285,28 +4285,28 @@
         <v>0.229</v>
       </c>
       <c r="M35">
-        <v>0.04082301300000001</v>
+        <v>0.042060074</v>
       </c>
       <c r="N35">
-        <v>0.188176987</v>
+        <v>0.186939926</v>
       </c>
       <c r="O35">
-        <v>0.03575362752999999</v>
+        <v>0.03551858593999999</v>
       </c>
       <c r="P35">
-        <v>0.15242335947</v>
+        <v>0.15142134006</v>
       </c>
       <c r="Q35">
-        <v>0.21142335947</v>
+        <v>0.21042134006</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1090291487975575</v>
+        <v>0.109857052455809</v>
       </c>
       <c r="T35">
-        <v>1.158064065387139</v>
+        <v>1.17322741163577</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.609581046847276</v>
+        <v>5.444593368998827</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08773527462083396</v>
+        <v>0.08763932954730436</v>
       </c>
       <c r="C36">
-        <v>1.45679323750288</v>
+        <v>1.438016798243082</v>
       </c>
       <c r="D36">
-        <v>2.21737323750288</v>
+        <v>2.220966798243083</v>
       </c>
       <c r="E36">
-        <v>-0.73942</v>
+        <v>-0.7170499999999999</v>
       </c>
       <c r="F36">
-        <v>0.76058</v>
+        <v>0.7829500000000001</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4367,28 +4367,28 @@
         <v>0.229</v>
       </c>
       <c r="M36">
-        <v>0.042060074</v>
+        <v>0.04329713500000001</v>
       </c>
       <c r="N36">
-        <v>0.186939926</v>
+        <v>0.185702865</v>
       </c>
       <c r="O36">
-        <v>0.03551858593999999</v>
+        <v>0.03528354434999999</v>
       </c>
       <c r="P36">
-        <v>0.15142134006</v>
+        <v>0.15041932065</v>
       </c>
       <c r="Q36">
-        <v>0.21042134006</v>
+        <v>0.20941932065</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.109857052455809</v>
+        <v>0.1107104300727759</v>
       </c>
       <c r="T36">
-        <v>1.17322741163577</v>
+        <v>1.188857322384359</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.444593368998827</v>
+        <v>5.289033558456002</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08763932954730436</v>
+        <v>0.08754338447377474</v>
       </c>
       <c r="C37">
-        <v>1.438016798243082</v>
+        <v>1.419252025617439</v>
       </c>
       <c r="D37">
-        <v>2.220966798243083</v>
+        <v>2.224572025617439</v>
       </c>
       <c r="E37">
-        <v>-0.7170499999999999</v>
+        <v>-0.6946799999999999</v>
       </c>
       <c r="F37">
-        <v>0.7829500000000001</v>
+        <v>0.8053200000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4449,28 +4449,28 @@
         <v>0.229</v>
       </c>
       <c r="M37">
-        <v>0.04329713500000001</v>
+        <v>0.04453419600000001</v>
       </c>
       <c r="N37">
-        <v>0.185702865</v>
+        <v>0.184465804</v>
       </c>
       <c r="O37">
-        <v>0.03528354434999999</v>
+        <v>0.03504850275999999</v>
       </c>
       <c r="P37">
-        <v>0.15041932065</v>
+        <v>0.14941730124</v>
       </c>
       <c r="Q37">
-        <v>0.20941932065</v>
+        <v>0.20841730124</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1107104300727759</v>
+        <v>0.1115904757402731</v>
       </c>
       <c r="T37">
-        <v>1.188857322384359</v>
+        <v>1.204975667843842</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.289033558456002</v>
+        <v>5.142115959610002</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08754338447377476</v>
+        <v>0.08744743940024516</v>
       </c>
       <c r="C38">
-        <v>1.419252025617438</v>
+        <v>1.400498976532593</v>
       </c>
       <c r="D38">
-        <v>2.224572025617438</v>
+        <v>2.228188976532593</v>
       </c>
       <c r="E38">
-        <v>-0.69468</v>
+        <v>-0.67231</v>
       </c>
       <c r="F38">
-        <v>0.80532</v>
+        <v>0.82769</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4531,28 +4531,28 @@
         <v>0.229</v>
       </c>
       <c r="M38">
-        <v>0.04453419600000001</v>
+        <v>0.045771257</v>
       </c>
       <c r="N38">
-        <v>0.184465804</v>
+        <v>0.183228743</v>
       </c>
       <c r="O38">
-        <v>0.03504850276</v>
+        <v>0.03481346117</v>
       </c>
       <c r="P38">
-        <v>0.14941730124</v>
+        <v>0.14841528183</v>
       </c>
       <c r="Q38">
-        <v>0.20841730124</v>
+        <v>0.20741528183</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1115904757402731</v>
+        <v>0.1124984593654685</v>
       </c>
       <c r="T38">
-        <v>1.204975667843841</v>
+        <v>1.221605706809975</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.142115959610003</v>
+        <v>5.003139852593517</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08744743940024516</v>
+        <v>0.08735149432671557</v>
       </c>
       <c r="C39">
-        <v>1.400498976532593</v>
+        <v>1.381757708265893</v>
       </c>
       <c r="D39">
-        <v>2.228188976532593</v>
+        <v>2.231817708265893</v>
       </c>
       <c r="E39">
-        <v>-0.67231</v>
+        <v>-0.64994</v>
       </c>
       <c r="F39">
-        <v>0.82769</v>
+        <v>0.85006</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4613,28 +4613,28 @@
         <v>0.229</v>
       </c>
       <c r="M39">
-        <v>0.045771257</v>
+        <v>0.047008318</v>
       </c>
       <c r="N39">
-        <v>0.183228743</v>
+        <v>0.181991682</v>
       </c>
       <c r="O39">
-        <v>0.03481346117</v>
+        <v>0.03457841958</v>
       </c>
       <c r="P39">
-        <v>0.14841528183</v>
+        <v>0.14741326242</v>
       </c>
       <c r="Q39">
-        <v>0.20741528183</v>
+        <v>0.20641326242</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1124984593654685</v>
+        <v>0.1134357327850251</v>
       </c>
       <c r="T39">
-        <v>1.221605706809975</v>
+        <v>1.238772198645983</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.003139852593517</v>
+        <v>4.871478277525267</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08735149432671557</v>
+        <v>0.08725554925318596</v>
       </c>
       <c r="C40">
-        <v>1.381757708265893</v>
+        <v>1.363028278468414</v>
       </c>
       <c r="D40">
-        <v>2.231817708265893</v>
+        <v>2.235458278468414</v>
       </c>
       <c r="E40">
-        <v>-0.64994</v>
+        <v>-0.62757</v>
       </c>
       <c r="F40">
-        <v>0.85006</v>
+        <v>0.87243</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4695,28 +4695,28 @@
         <v>0.229</v>
       </c>
       <c r="M40">
-        <v>0.047008318</v>
+        <v>0.048245379</v>
       </c>
       <c r="N40">
-        <v>0.181991682</v>
+        <v>0.180754621</v>
       </c>
       <c r="O40">
-        <v>0.03457841958</v>
+        <v>0.03434337798999999</v>
       </c>
       <c r="P40">
-        <v>0.14741326242</v>
+        <v>0.14641124301</v>
       </c>
       <c r="Q40">
-        <v>0.20641326242</v>
+        <v>0.20541124301</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1134357327850251</v>
+        <v>0.1144037364806327</v>
       </c>
       <c r="T40">
-        <v>1.238772198645983</v>
+        <v>1.256501526279893</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.871478277525267</v>
+        <v>4.746568578101542</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08725554925318596</v>
+        <v>0.08715960417965637</v>
       </c>
       <c r="C41">
-        <v>1.363028278468414</v>
+        <v>1.344310745168005</v>
       </c>
       <c r="D41">
-        <v>2.235458278468414</v>
+        <v>2.239110745168005</v>
       </c>
       <c r="E41">
-        <v>-0.62757</v>
+        <v>-0.6052</v>
       </c>
       <c r="F41">
-        <v>0.87243</v>
+        <v>0.8948</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4777,28 +4777,28 @@
         <v>0.229</v>
       </c>
       <c r="M41">
-        <v>0.048245379</v>
+        <v>0.04948244</v>
       </c>
       <c r="N41">
-        <v>0.180754621</v>
+        <v>0.17951756</v>
       </c>
       <c r="O41">
-        <v>0.03434337798999999</v>
+        <v>0.03410833639999999</v>
       </c>
       <c r="P41">
-        <v>0.14641124301</v>
+        <v>0.1454092236</v>
       </c>
       <c r="Q41">
-        <v>0.20541124301</v>
+        <v>0.2044092236</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1144037364806327</v>
+        <v>0.115404006966094</v>
       </c>
       <c r="T41">
-        <v>1.256501526279893</v>
+        <v>1.2748218315016</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.746568578101542</v>
+        <v>4.627904363649002</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08715960417965637</v>
+        <v>0.08706365910612679</v>
       </c>
       <c r="C42">
-        <v>1.344310745168005</v>
+        <v>1.325605166772383</v>
       </c>
       <c r="D42">
-        <v>2.239110745168005</v>
+        <v>2.242775166772383</v>
       </c>
       <c r="E42">
-        <v>-0.6052</v>
+        <v>-0.5828299999999998</v>
       </c>
       <c r="F42">
-        <v>0.8948</v>
+        <v>0.9171700000000002</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4859,28 +4859,28 @@
         <v>0.229</v>
       </c>
       <c r="M42">
-        <v>0.04948244</v>
+        <v>0.05071950100000001</v>
       </c>
       <c r="N42">
-        <v>0.17951756</v>
+        <v>0.178280499</v>
       </c>
       <c r="O42">
-        <v>0.03410833639999999</v>
+        <v>0.03387329481</v>
       </c>
       <c r="P42">
-        <v>0.1454092236</v>
+        <v>0.14440720419</v>
       </c>
       <c r="Q42">
-        <v>0.2044092236</v>
+        <v>0.20340720419</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.115404006966094</v>
+        <v>0.1164381849256386</v>
       </c>
       <c r="T42">
-        <v>1.2748218315016</v>
+        <v>1.293763164018958</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.627904363649002</v>
+        <v>4.515028647462442</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08706365910612679</v>
+        <v>0.08781821403259718</v>
       </c>
       <c r="C43">
-        <v>1.325605166772383</v>
+        <v>1.27473615355324</v>
       </c>
       <c r="D43">
-        <v>2.242775166772383</v>
+        <v>2.21427615355324</v>
       </c>
       <c r="E43">
-        <v>-0.5828299999999998</v>
+        <v>-0.5604599999999998</v>
       </c>
       <c r="F43">
-        <v>0.9171700000000002</v>
+        <v>0.9395400000000002</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4941,45 +4941,45 @@
         <v>0.229</v>
       </c>
       <c r="M43">
-        <v>0.05071950100000001</v>
+        <v>0.05430541200000001</v>
       </c>
       <c r="N43">
-        <v>0.178280499</v>
+        <v>0.174694588</v>
       </c>
       <c r="O43">
-        <v>0.03387329481</v>
+        <v>0.03319197172</v>
       </c>
       <c r="P43">
-        <v>0.14440720419</v>
+        <v>0.14150261628</v>
       </c>
       <c r="Q43">
-        <v>0.20340720419</v>
+        <v>0.20050261628</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1164381849256386</v>
+        <v>0.1175080241941331</v>
       </c>
       <c r="T43">
-        <v>1.293763164018958</v>
+        <v>1.313357645933466</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.515028647462442</v>
+        <v>4.216890942655954</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08781821403259718</v>
+        <v>0.08774251895906759</v>
       </c>
       <c r="C44">
-        <v>1.27473615355324</v>
+        <v>1.255192377604981</v>
       </c>
       <c r="D44">
-        <v>2.21427615355324</v>
+        <v>2.217102377604981</v>
       </c>
       <c r="E44">
-        <v>-0.56046</v>
+        <v>-0.53809</v>
       </c>
       <c r="F44">
-        <v>0.93954</v>
+        <v>0.96191</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5023,28 +5023,28 @@
         <v>0.229</v>
       </c>
       <c r="M44">
-        <v>0.054305412</v>
+        <v>0.05559839800000001</v>
       </c>
       <c r="N44">
-        <v>0.174694588</v>
+        <v>0.173401602</v>
       </c>
       <c r="O44">
-        <v>0.03319197172</v>
+        <v>0.03294630438</v>
       </c>
       <c r="P44">
-        <v>0.14150261628</v>
+        <v>0.14045529762</v>
       </c>
       <c r="Q44">
-        <v>0.20050261628</v>
+        <v>0.19945529762</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1175080241941331</v>
+        <v>0.1186154016825747</v>
       </c>
       <c r="T44">
-        <v>1.313357645933466</v>
+        <v>1.333639653529185</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.216890942655954</v>
+        <v>4.118823711431397</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08774251895906759</v>
+        <v>0.08766682388553801</v>
       </c>
       <c r="C45">
-        <v>1.255192377604981</v>
+        <v>1.235655825462501</v>
       </c>
       <c r="D45">
-        <v>2.217102377604981</v>
+        <v>2.219935825462501</v>
       </c>
       <c r="E45">
-        <v>-0.53809</v>
+        <v>-0.51572</v>
       </c>
       <c r="F45">
-        <v>0.96191</v>
+        <v>0.98428</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5105,28 +5105,28 @@
         <v>0.229</v>
       </c>
       <c r="M45">
-        <v>0.05559839800000001</v>
+        <v>0.056891384</v>
       </c>
       <c r="N45">
-        <v>0.173401602</v>
+        <v>0.172108616</v>
       </c>
       <c r="O45">
-        <v>0.03294630438</v>
+        <v>0.03270063704</v>
       </c>
       <c r="P45">
-        <v>0.14045529762</v>
+        <v>0.13940797896</v>
       </c>
       <c r="Q45">
-        <v>0.19945529762</v>
+        <v>0.19840797896</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1186154016825747</v>
+        <v>0.1197623283670321</v>
       </c>
       <c r="T45">
-        <v>1.333639653529185</v>
+        <v>1.354646018539038</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.118823711431397</v>
+        <v>4.025214081626139</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08766682388553801</v>
+        <v>0.0888668788120084</v>
       </c>
       <c r="C46">
-        <v>1.235655825462501</v>
+        <v>1.169200700272919</v>
       </c>
       <c r="D46">
-        <v>2.219935825462501</v>
+        <v>2.175850700272919</v>
       </c>
       <c r="E46">
-        <v>-0.51572</v>
+        <v>-0.49335</v>
       </c>
       <c r="F46">
-        <v>0.98428</v>
+        <v>1.00665</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5187,45 +5187,45 @@
         <v>0.229</v>
       </c>
       <c r="M46">
-        <v>0.056891384</v>
+        <v>0.06170764500000001</v>
       </c>
       <c r="N46">
-        <v>0.172108616</v>
+        <v>0.167292355</v>
       </c>
       <c r="O46">
-        <v>0.03270063704</v>
+        <v>0.03178554744999999</v>
       </c>
       <c r="P46">
-        <v>0.13940797896</v>
+        <v>0.13550680755</v>
       </c>
       <c r="Q46">
-        <v>0.19840797896</v>
+        <v>0.19450680755</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1197623283670321</v>
+        <v>0.1209509614763789</v>
       </c>
       <c r="T46">
-        <v>1.354646018539038</v>
+        <v>1.37641625136743</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.19</v>
       </c>
       <c r="W46">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.025214081626139</v>
+        <v>3.711047472318867</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0888668788120084</v>
+        <v>0.0888195337384788</v>
       </c>
       <c r="C47">
-        <v>1.169200700272919</v>
+        <v>1.148536762290445</v>
       </c>
       <c r="D47">
-        <v>2.175850700272919</v>
+        <v>2.177556762290445</v>
       </c>
       <c r="E47">
-        <v>-0.49335</v>
+        <v>-0.47098</v>
       </c>
       <c r="F47">
-        <v>1.00665</v>
+        <v>1.02902</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5269,28 +5269,28 @@
         <v>0.229</v>
       </c>
       <c r="M47">
-        <v>0.06170764500000001</v>
+        <v>0.06307892600000001</v>
       </c>
       <c r="N47">
-        <v>0.167292355</v>
+        <v>0.165921074</v>
       </c>
       <c r="O47">
-        <v>0.03178554744999999</v>
+        <v>0.03152500405999999</v>
       </c>
       <c r="P47">
-        <v>0.13550680755</v>
+        <v>0.13439606994</v>
       </c>
       <c r="Q47">
-        <v>0.19450680755</v>
+        <v>0.19339606994</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1209509614763789</v>
+        <v>0.12218361803422</v>
       </c>
       <c r="T47">
-        <v>1.37641625136743</v>
+        <v>1.398992789115392</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.711047472318867</v>
+        <v>3.630372527268456</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0888195337384788</v>
+        <v>0.08877218866494921</v>
       </c>
       <c r="C48">
-        <v>1.148536762290445</v>
+        <v>1.127875501818525</v>
       </c>
       <c r="D48">
-        <v>2.177556762290445</v>
+        <v>2.179265501818525</v>
       </c>
       <c r="E48">
-        <v>-0.47098</v>
+        <v>-0.44861</v>
       </c>
       <c r="F48">
-        <v>1.02902</v>
+        <v>1.05139</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5351,28 +5351,28 @@
         <v>0.229</v>
       </c>
       <c r="M48">
-        <v>0.06307892600000001</v>
+        <v>0.06445020700000001</v>
       </c>
       <c r="N48">
-        <v>0.165921074</v>
+        <v>0.164549793</v>
       </c>
       <c r="O48">
-        <v>0.03152500405999999</v>
+        <v>0.03126446066999999</v>
       </c>
       <c r="P48">
-        <v>0.13439606994</v>
+        <v>0.13328533233</v>
       </c>
       <c r="Q48">
-        <v>0.19339606994</v>
+        <v>0.19228533233</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.12218361803422</v>
+        <v>0.1234627899338664</v>
       </c>
       <c r="T48">
-        <v>1.398992789115392</v>
+        <v>1.422421271684032</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.630372527268456</v>
+        <v>3.55313055860317</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08877218866494921</v>
+        <v>0.08981348359141961</v>
       </c>
       <c r="C49">
-        <v>1.127875501818525</v>
+        <v>1.068532550741687</v>
       </c>
       <c r="D49">
-        <v>2.179265501818525</v>
+        <v>2.142292550741687</v>
       </c>
       <c r="E49">
-        <v>-0.44861</v>
+        <v>-0.42624</v>
       </c>
       <c r="F49">
-        <v>1.05139</v>
+        <v>1.07376</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5433,45 +5433,45 @@
         <v>0.229</v>
       </c>
       <c r="M49">
-        <v>0.06445020700000001</v>
+        <v>0.06882801600000001</v>
       </c>
       <c r="N49">
-        <v>0.164549793</v>
+        <v>0.160171984</v>
       </c>
       <c r="O49">
-        <v>0.03126446066999999</v>
+        <v>0.03043267696</v>
       </c>
       <c r="P49">
-        <v>0.13328533233</v>
+        <v>0.12973930704</v>
       </c>
       <c r="Q49">
-        <v>0.19228533233</v>
+        <v>0.18873930704</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1234627899338664</v>
+        <v>0.12479116075273</v>
       </c>
       <c r="T49">
-        <v>1.422421271684032</v>
+        <v>1.446750849736081</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.19</v>
       </c>
       <c r="W49">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.55313055860317</v>
+        <v>3.327133532368563</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08981348359141961</v>
+        <v>0.08978881851789002</v>
       </c>
       <c r="C50">
-        <v>1.068532550741687</v>
+        <v>1.047023814109558</v>
       </c>
       <c r="D50">
-        <v>2.142292550741687</v>
+        <v>2.143153814109558</v>
       </c>
       <c r="E50">
-        <v>-0.42624</v>
+        <v>-0.40387</v>
       </c>
       <c r="F50">
-        <v>1.07376</v>
+        <v>1.09613</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5515,28 +5515,28 @@
         <v>0.229</v>
       </c>
       <c r="M50">
-        <v>0.06882801600000001</v>
+        <v>0.07026193300000001</v>
       </c>
       <c r="N50">
-        <v>0.160171984</v>
+        <v>0.158738067</v>
       </c>
       <c r="O50">
-        <v>0.03043267696</v>
+        <v>0.03016023273</v>
       </c>
       <c r="P50">
-        <v>0.12973930704</v>
+        <v>0.12857783427</v>
       </c>
       <c r="Q50">
-        <v>0.18873930704</v>
+        <v>0.18757783427</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.12479116075273</v>
+        <v>0.1261716245448824</v>
       </c>
       <c r="T50">
-        <v>1.446750849736081</v>
+        <v>1.472034528888211</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.327133532368563</v>
+        <v>3.259232848034511</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08978881851789002</v>
+        <v>0.08976415344436042</v>
       </c>
       <c r="C51">
-        <v>1.047023814109558</v>
+        <v>1.025515770261356</v>
       </c>
       <c r="D51">
-        <v>2.143153814109558</v>
+        <v>2.144015770261356</v>
       </c>
       <c r="E51">
-        <v>-0.40387</v>
+        <v>-0.3815</v>
       </c>
       <c r="F51">
-        <v>1.09613</v>
+        <v>1.1185</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5597,28 +5597,28 @@
         <v>0.229</v>
       </c>
       <c r="M51">
-        <v>0.07026193300000001</v>
+        <v>0.07169585000000001</v>
       </c>
       <c r="N51">
-        <v>0.158738067</v>
+        <v>0.15730415</v>
       </c>
       <c r="O51">
-        <v>0.03016023273</v>
+        <v>0.02988778849999999</v>
       </c>
       <c r="P51">
-        <v>0.12857783427</v>
+        <v>0.1274163615</v>
       </c>
       <c r="Q51">
-        <v>0.18757783427</v>
+        <v>0.1864163615</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1261716245448824</v>
+        <v>0.1276073068887208</v>
       </c>
       <c r="T51">
-        <v>1.472034528888211</v>
+        <v>1.498329555206426</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.259232848034511</v>
+        <v>3.19404819107382</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08976415344436042</v>
+        <v>0.08973948837083082</v>
       </c>
       <c r="C52">
-        <v>1.025515770261356</v>
+        <v>1.004008420033312</v>
       </c>
       <c r="D52">
-        <v>2.144015770261356</v>
+        <v>2.144878420033312</v>
       </c>
       <c r="E52">
-        <v>-0.3815</v>
+        <v>-0.3591299999999999</v>
       </c>
       <c r="F52">
-        <v>1.1185</v>
+        <v>1.14087</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5679,28 +5679,28 @@
         <v>0.229</v>
       </c>
       <c r="M52">
-        <v>0.07169585000000001</v>
+        <v>0.07312976700000001</v>
       </c>
       <c r="N52">
-        <v>0.15730415</v>
+        <v>0.155870233</v>
       </c>
       <c r="O52">
-        <v>0.02988778849999999</v>
+        <v>0.02961534426999999</v>
       </c>
       <c r="P52">
-        <v>0.1274163615</v>
+        <v>0.12625488873</v>
       </c>
       <c r="Q52">
-        <v>0.1864163615</v>
+        <v>0.18525488873</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1276073068887208</v>
+        <v>0.1291015885118996</v>
       </c>
       <c r="T52">
-        <v>1.498329555206426</v>
+        <v>1.525697847904976</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.19404819107382</v>
+        <v>3.131419795170412</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08973948837083082</v>
+        <v>0.08971482329730124</v>
       </c>
       <c r="C53">
-        <v>1.004008420033312</v>
+        <v>0.9825017642630001</v>
       </c>
       <c r="D53">
-        <v>2.144878420033312</v>
+        <v>2.145741764263</v>
       </c>
       <c r="E53">
-        <v>-0.3591299999999999</v>
+        <v>-0.3367599999999999</v>
       </c>
       <c r="F53">
-        <v>1.14087</v>
+        <v>1.16324</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5761,28 +5761,28 @@
         <v>0.229</v>
       </c>
       <c r="M53">
-        <v>0.07312976700000001</v>
+        <v>0.07456368400000001</v>
       </c>
       <c r="N53">
-        <v>0.155870233</v>
+        <v>0.154436316</v>
       </c>
       <c r="O53">
-        <v>0.02961534426999999</v>
+        <v>0.02934290003999999</v>
       </c>
       <c r="P53">
-        <v>0.12625488873</v>
+        <v>0.12509341596</v>
       </c>
       <c r="Q53">
-        <v>0.18525488873</v>
+        <v>0.18409341596</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1291015885118996</v>
+        <v>0.1306581318693776</v>
       </c>
       <c r="T53">
-        <v>1.525697847904976</v>
+        <v>1.554206486132632</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.131419795170412</v>
+        <v>3.071200183724827</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08971482329730124</v>
+        <v>0.08969015822377163</v>
       </c>
       <c r="C54">
-        <v>0.9825017642630001</v>
+        <v>0.960995803789348</v>
       </c>
       <c r="D54">
-        <v>2.145741764263</v>
+        <v>2.146605803789348</v>
       </c>
       <c r="E54">
-        <v>-0.3367599999999999</v>
+        <v>-0.3143899999999999</v>
       </c>
       <c r="F54">
-        <v>1.16324</v>
+        <v>1.18561</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5843,28 +5843,28 @@
         <v>0.229</v>
       </c>
       <c r="M54">
-        <v>0.07456368400000001</v>
+        <v>0.07599760100000001</v>
       </c>
       <c r="N54">
-        <v>0.154436316</v>
+        <v>0.153002399</v>
       </c>
       <c r="O54">
-        <v>0.02934290003999999</v>
+        <v>0.02907045580999999</v>
       </c>
       <c r="P54">
-        <v>0.12509341596</v>
+        <v>0.12393194319</v>
       </c>
       <c r="Q54">
-        <v>0.18409341596</v>
+        <v>0.1829319431899999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1306581318693776</v>
+        <v>0.1322809111144077</v>
       </c>
       <c r="T54">
-        <v>1.554206486132632</v>
+        <v>1.583928257901891</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.071200183724827</v>
+        <v>3.013253010447</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08969015822377163</v>
+        <v>0.09307721315024203</v>
       </c>
       <c r="C55">
-        <v>0.960995803789348</v>
+        <v>0.8261461762830256</v>
       </c>
       <c r="D55">
-        <v>2.146605803789348</v>
+        <v>2.034126176283026</v>
       </c>
       <c r="E55">
-        <v>-0.3143899999999999</v>
+        <v>-0.2920199999999999</v>
       </c>
       <c r="F55">
-        <v>1.18561</v>
+        <v>1.20798</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5925,45 +5925,45 @@
         <v>0.229</v>
       </c>
       <c r="M55">
-        <v>0.07599760100000001</v>
+        <v>0.08685376200000001</v>
       </c>
       <c r="N55">
-        <v>0.153002399</v>
+        <v>0.142146238</v>
       </c>
       <c r="O55">
-        <v>0.02907045580999999</v>
+        <v>0.02700778522</v>
       </c>
       <c r="P55">
-        <v>0.12393194319</v>
+        <v>0.11513845278</v>
       </c>
       <c r="Q55">
-        <v>0.1829319431899999</v>
+        <v>0.17413845278</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1322809111144077</v>
+        <v>0.133974245978787</v>
       </c>
       <c r="T55">
-        <v>1.583928257901891</v>
+        <v>1.614942280617639</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.19</v>
       </c>
       <c r="W55">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.013253010447</v>
+        <v>2.636615786429608</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09307721315024203</v>
+        <v>0.09311572807671244</v>
       </c>
       <c r="C56">
-        <v>0.8261461762830256</v>
+        <v>0.8025648877658766</v>
       </c>
       <c r="D56">
-        <v>2.034126176283026</v>
+        <v>2.032914887765877</v>
       </c>
       <c r="E56">
-        <v>-0.2920199999999999</v>
+        <v>-0.2696499999999999</v>
       </c>
       <c r="F56">
-        <v>1.20798</v>
+        <v>1.23035</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -6007,28 +6007,28 @@
         <v>0.229</v>
       </c>
       <c r="M56">
-        <v>0.08685376200000001</v>
+        <v>0.08846216500000001</v>
       </c>
       <c r="N56">
-        <v>0.142146238</v>
+        <v>0.140537835</v>
       </c>
       <c r="O56">
-        <v>0.02700778522</v>
+        <v>0.02670218865</v>
       </c>
       <c r="P56">
-        <v>0.11513845278</v>
+        <v>0.11383564635</v>
       </c>
       <c r="Q56">
-        <v>0.17413845278</v>
+        <v>0.17283564635</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.133974245978787</v>
+        <v>0.1357428401704721</v>
       </c>
       <c r="T56">
-        <v>1.614942280617639</v>
+        <v>1.647334704342976</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.636615786429608</v>
+        <v>2.588677317585433</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09311572807671244</v>
+        <v>0.09315424300318284</v>
       </c>
       <c r="C57">
-        <v>0.8025648877658766</v>
+        <v>0.7789850409947745</v>
       </c>
       <c r="D57">
-        <v>2.032914887765877</v>
+        <v>2.031705040994775</v>
       </c>
       <c r="E57">
-        <v>-0.2696499999999999</v>
+        <v>-0.2472799999999997</v>
       </c>
       <c r="F57">
-        <v>1.23035</v>
+        <v>1.25272</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -6089,28 +6089,28 @@
         <v>0.229</v>
       </c>
       <c r="M57">
-        <v>0.08846216500000001</v>
+        <v>0.09007056800000003</v>
       </c>
       <c r="N57">
-        <v>0.140537835</v>
+        <v>0.138929432</v>
       </c>
       <c r="O57">
-        <v>0.02670218865</v>
+        <v>0.02639659207999999</v>
       </c>
       <c r="P57">
-        <v>0.11383564635</v>
+        <v>0.11253283992</v>
       </c>
       <c r="Q57">
-        <v>0.17283564635</v>
+        <v>0.17153283992</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1357428401704721</v>
+        <v>0.1375918250072337</v>
       </c>
       <c r="T57">
-        <v>1.647334704342976</v>
+        <v>1.68119951096492</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.588677317585433</v>
+        <v>2.542450936914264</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09315424300318284</v>
+        <v>0.09499338792965326</v>
       </c>
       <c r="C58">
-        <v>0.7789850409947745</v>
+        <v>0.7004729069208622</v>
       </c>
       <c r="D58">
-        <v>2.031705040994775</v>
+        <v>1.975562906920862</v>
       </c>
       <c r="E58">
-        <v>-0.2472799999999997</v>
+        <v>-0.2249099999999997</v>
       </c>
       <c r="F58">
-        <v>1.25272</v>
+        <v>1.27509</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6171,45 +6171,45 @@
         <v>0.229</v>
       </c>
       <c r="M58">
-        <v>0.09007056800000003</v>
+        <v>0.09665182200000003</v>
       </c>
       <c r="N58">
-        <v>0.138929432</v>
+        <v>0.132348178</v>
       </c>
       <c r="O58">
-        <v>0.02639659207999999</v>
+        <v>0.02514615381999999</v>
       </c>
       <c r="P58">
-        <v>0.11253283992</v>
+        <v>0.10720202418</v>
       </c>
       <c r="Q58">
-        <v>0.17153283992</v>
+        <v>0.16620202418</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1375918250072337</v>
+        <v>0.1395268091387285</v>
       </c>
       <c r="T58">
-        <v>1.68119951096492</v>
+        <v>1.716639424871605</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.19</v>
       </c>
       <c r="W58">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.542450936914264</v>
+        <v>2.369329364530758</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09499338792965326</v>
+        <v>0.09506349285612364</v>
       </c>
       <c r="C59">
-        <v>0.7004729069208622</v>
+        <v>0.6760241940936751</v>
       </c>
       <c r="D59">
-        <v>1.975562906920862</v>
+        <v>1.973484194093675</v>
       </c>
       <c r="E59">
-        <v>-0.2249099999999997</v>
+        <v>-0.2025399999999997</v>
       </c>
       <c r="F59">
-        <v>1.27509</v>
+        <v>1.29746</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6253,28 +6253,28 @@
         <v>0.229</v>
       </c>
       <c r="M59">
-        <v>0.09665182200000003</v>
+        <v>0.09834746800000004</v>
       </c>
       <c r="N59">
-        <v>0.132348178</v>
+        <v>0.1306525319999999</v>
       </c>
       <c r="O59">
-        <v>0.02514615381999999</v>
+        <v>0.02482398107999999</v>
       </c>
       <c r="P59">
-        <v>0.10720202418</v>
+        <v>0.1058285509199999</v>
       </c>
       <c r="Q59">
-        <v>0.16620202418</v>
+        <v>0.1648285509199999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1395268091387285</v>
+        <v>0.141553935371723</v>
       </c>
       <c r="T59">
-        <v>1.716639424871605</v>
+        <v>1.753766953726227</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.369329364530758</v>
+        <v>2.328478858245744</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09506349285612364</v>
+        <v>0.09513359778259406</v>
       </c>
       <c r="C60">
-        <v>0.6760241940936753</v>
+        <v>0.651579851165436</v>
       </c>
       <c r="D60">
-        <v>1.973484194093675</v>
+        <v>1.971409851165436</v>
       </c>
       <c r="E60">
-        <v>-0.2025399999999999</v>
+        <v>-0.1801699999999999</v>
       </c>
       <c r="F60">
-        <v>1.29746</v>
+        <v>1.31983</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6335,28 +6335,28 @@
         <v>0.229</v>
       </c>
       <c r="M60">
-        <v>0.09834746800000001</v>
+        <v>0.100043114</v>
       </c>
       <c r="N60">
-        <v>0.130652532</v>
+        <v>0.128956886</v>
       </c>
       <c r="O60">
-        <v>0.02482398108</v>
+        <v>0.02450180833999999</v>
       </c>
       <c r="P60">
-        <v>0.10582855092</v>
+        <v>0.10445507766</v>
       </c>
       <c r="Q60">
-        <v>0.16482855092</v>
+        <v>0.16345507766</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1415539353717229</v>
+        <v>0.143679945811205</v>
       </c>
       <c r="T60">
-        <v>1.753766953726226</v>
+        <v>1.792705581549367</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.328478858245745</v>
+        <v>2.289013114885647</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09513359778259406</v>
+        <v>0.09520370270906445</v>
       </c>
       <c r="C61">
-        <v>0.651579851165436</v>
+        <v>0.6271398643709225</v>
       </c>
       <c r="D61">
-        <v>1.971409851165436</v>
+        <v>1.969339864370923</v>
       </c>
       <c r="E61">
-        <v>-0.1801699999999999</v>
+        <v>-0.1577999999999999</v>
       </c>
       <c r="F61">
-        <v>1.31983</v>
+        <v>1.3422</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6417,28 +6417,28 @@
         <v>0.229</v>
       </c>
       <c r="M61">
-        <v>0.100043114</v>
+        <v>0.10173876</v>
       </c>
       <c r="N61">
-        <v>0.128956886</v>
+        <v>0.12726124</v>
       </c>
       <c r="O61">
-        <v>0.02450180833999999</v>
+        <v>0.0241796356</v>
       </c>
       <c r="P61">
-        <v>0.10445507766</v>
+        <v>0.1030816044</v>
       </c>
       <c r="Q61">
-        <v>0.16345507766</v>
+        <v>0.1620816044</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.143679945811205</v>
+        <v>0.1459122567726611</v>
       </c>
       <c r="T61">
-        <v>1.792705581549367</v>
+        <v>1.833591140763664</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.289013114885647</v>
+        <v>2.25086289630422</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09520370270906445</v>
+        <v>0.09527380763553486</v>
       </c>
       <c r="C62">
-        <v>0.6271398643709225</v>
+        <v>0.6027042200026611</v>
       </c>
       <c r="D62">
-        <v>1.969339864370923</v>
+        <v>1.967274220002661</v>
       </c>
       <c r="E62">
-        <v>-0.1577999999999999</v>
+        <v>-0.1354299999999999</v>
       </c>
       <c r="F62">
-        <v>1.3422</v>
+        <v>1.36457</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6499,28 +6499,28 @@
         <v>0.229</v>
       </c>
       <c r="M62">
-        <v>0.10173876</v>
+        <v>0.103434406</v>
       </c>
       <c r="N62">
-        <v>0.12726124</v>
+        <v>0.125565594</v>
       </c>
       <c r="O62">
-        <v>0.0241796356</v>
+        <v>0.02385746285999999</v>
       </c>
       <c r="P62">
-        <v>0.1030816044</v>
+        <v>0.10170813114</v>
       </c>
       <c r="Q62">
-        <v>0.1620816044</v>
+        <v>0.16070813114</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1459122567726611</v>
+        <v>0.1482590452193201</v>
       </c>
       <c r="T62">
-        <v>1.833591140763664</v>
+        <v>1.876573395322285</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.25086289630422</v>
+        <v>2.213963504561528</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09527380763553486</v>
+        <v>0.09534391256200526</v>
       </c>
       <c r="C63">
-        <v>0.6027042200026611</v>
+        <v>0.5782729044106336</v>
       </c>
       <c r="D63">
-        <v>1.967274220002661</v>
+        <v>1.965212904410634</v>
       </c>
       <c r="E63">
-        <v>-0.1354299999999999</v>
+        <v>-0.1130599999999999</v>
       </c>
       <c r="F63">
-        <v>1.36457</v>
+        <v>1.38694</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6581,28 +6581,28 @@
         <v>0.229</v>
       </c>
       <c r="M63">
-        <v>0.103434406</v>
+        <v>0.105130052</v>
       </c>
       <c r="N63">
-        <v>0.125565594</v>
+        <v>0.123869948</v>
       </c>
       <c r="O63">
-        <v>0.02385746285999999</v>
+        <v>0.02353529011999999</v>
       </c>
       <c r="P63">
-        <v>0.10170813114</v>
+        <v>0.10033465788</v>
       </c>
       <c r="Q63">
-        <v>0.16070813114</v>
+        <v>0.15933465788</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1482590452193201</v>
+        <v>0.1507293488473823</v>
       </c>
       <c r="T63">
-        <v>1.876573395322285</v>
+        <v>1.921817873805043</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.213963504561528</v>
+        <v>2.178254415778277</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09534391256200526</v>
+        <v>0.09541401748847567</v>
       </c>
       <c r="C64">
-        <v>0.5782729044106336</v>
+        <v>0.5538459040019694</v>
       </c>
       <c r="D64">
-        <v>1.965212904410634</v>
+        <v>1.963155904001969</v>
       </c>
       <c r="E64">
-        <v>-0.1130599999999999</v>
+        <v>-0.09068999999999994</v>
       </c>
       <c r="F64">
-        <v>1.38694</v>
+        <v>1.40931</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6663,28 +6663,28 @@
         <v>0.229</v>
       </c>
       <c r="M64">
-        <v>0.105130052</v>
+        <v>0.106825698</v>
       </c>
       <c r="N64">
-        <v>0.123869948</v>
+        <v>0.122174302</v>
       </c>
       <c r="O64">
-        <v>0.02353529011999999</v>
+        <v>0.02321311738</v>
       </c>
       <c r="P64">
-        <v>0.10033465788</v>
+        <v>0.09896118461999998</v>
       </c>
       <c r="Q64">
-        <v>0.15933465788</v>
+        <v>0.15796118462</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1507293488473823</v>
+        <v>0.1533331824012855</v>
       </c>
       <c r="T64">
-        <v>1.921817873805043</v>
+        <v>1.969507999773356</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.178254415778277</v>
+        <v>2.143678948861163</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09541401748847567</v>
+        <v>0.09548412241494607</v>
       </c>
       <c r="C65">
-        <v>0.5538459040019694</v>
+        <v>0.52942320524065</v>
       </c>
       <c r="D65">
-        <v>1.963155904001969</v>
+        <v>1.96110320524065</v>
       </c>
       <c r="E65">
-        <v>-0.09068999999999994</v>
+        <v>-0.06831999999999994</v>
       </c>
       <c r="F65">
-        <v>1.40931</v>
+        <v>1.43168</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6745,28 +6745,28 @@
         <v>0.229</v>
       </c>
       <c r="M65">
-        <v>0.106825698</v>
+        <v>0.108521344</v>
       </c>
       <c r="N65">
-        <v>0.122174302</v>
+        <v>0.120478656</v>
       </c>
       <c r="O65">
-        <v>0.02321311738</v>
+        <v>0.02289094463999999</v>
       </c>
       <c r="P65">
-        <v>0.09896118461999998</v>
+        <v>0.09758771135999997</v>
       </c>
       <c r="Q65">
-        <v>0.15796118462</v>
+        <v>0.15658771136</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1533331824012855</v>
+        <v>0.1560816733748502</v>
       </c>
       <c r="T65">
-        <v>1.969507999773356</v>
+        <v>2.019847577184353</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.143678948861163</v>
+        <v>2.110183965285207</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09548412241494607</v>
+        <v>0.09555422734141647</v>
       </c>
       <c r="C66">
-        <v>0.52942320524065</v>
+        <v>0.5050047946472112</v>
       </c>
       <c r="D66">
-        <v>1.96110320524065</v>
+        <v>1.959054794647211</v>
       </c>
       <c r="E66">
-        <v>-0.06831999999999994</v>
+        <v>-0.04594999999999994</v>
       </c>
       <c r="F66">
-        <v>1.43168</v>
+        <v>1.45405</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6827,28 +6827,28 @@
         <v>0.229</v>
       </c>
       <c r="M66">
-        <v>0.108521344</v>
+        <v>0.11021699</v>
       </c>
       <c r="N66">
-        <v>0.120478656</v>
+        <v>0.11878301</v>
       </c>
       <c r="O66">
-        <v>0.02289094463999999</v>
+        <v>0.02256877189999999</v>
       </c>
       <c r="P66">
-        <v>0.09758771135999997</v>
+        <v>0.09621423809999997</v>
       </c>
       <c r="Q66">
-        <v>0.15658771136</v>
+        <v>0.1552142381</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1560816733748502</v>
+        <v>0.1589872209754756</v>
       </c>
       <c r="T66">
-        <v>2.019847577184353</v>
+        <v>2.073063701875978</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.110183965285207</v>
+        <v>2.077719596588511</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09555422734141647</v>
+        <v>0.09562433226788689</v>
       </c>
       <c r="C67">
-        <v>0.5050047946472112</v>
+        <v>0.4805906587984483</v>
       </c>
       <c r="D67">
-        <v>1.959054794647211</v>
+        <v>1.957010658798448</v>
       </c>
       <c r="E67">
-        <v>-0.04594999999999994</v>
+        <v>-0.02357999999999993</v>
       </c>
       <c r="F67">
-        <v>1.45405</v>
+        <v>1.47642</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6909,28 +6909,28 @@
         <v>0.229</v>
       </c>
       <c r="M67">
-        <v>0.11021699</v>
+        <v>0.111912636</v>
       </c>
       <c r="N67">
-        <v>0.11878301</v>
+        <v>0.117087364</v>
       </c>
       <c r="O67">
-        <v>0.02256877189999999</v>
+        <v>0.02224659915999999</v>
       </c>
       <c r="P67">
-        <v>0.09621423809999997</v>
+        <v>0.09484076483999998</v>
       </c>
       <c r="Q67">
-        <v>0.1552142381</v>
+        <v>0.15384076484</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1589872209754756</v>
+        <v>0.1620636831408438</v>
       </c>
       <c r="T67">
-        <v>2.073063701875978</v>
+        <v>2.129410186843582</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.077719596588511</v>
+        <v>2.0462389966402</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09562433226788689</v>
+        <v>0.09569443719435727</v>
       </c>
       <c r="C68">
-        <v>0.4805906587984483</v>
+        <v>0.4561807843271244</v>
       </c>
       <c r="D68">
-        <v>1.957010658798448</v>
+        <v>1.954970784327124</v>
       </c>
       <c r="E68">
-        <v>-0.02357999999999993</v>
+        <v>-0.001209999999999933</v>
       </c>
       <c r="F68">
-        <v>1.47642</v>
+        <v>1.49879</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6991,28 +6991,28 @@
         <v>0.229</v>
       </c>
       <c r="M68">
-        <v>0.111912636</v>
+        <v>0.113608282</v>
       </c>
       <c r="N68">
-        <v>0.117087364</v>
+        <v>0.115391718</v>
       </c>
       <c r="O68">
-        <v>0.02224659915999999</v>
+        <v>0.02192442641999999</v>
       </c>
       <c r="P68">
-        <v>0.09484076483999998</v>
+        <v>0.09346729157999997</v>
       </c>
       <c r="Q68">
-        <v>0.15384076484</v>
+        <v>0.15246729158</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1620636831408438</v>
+        <v>0.1653265975586584</v>
       </c>
       <c r="T68">
-        <v>2.129410186843582</v>
+        <v>2.189171610294069</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.0462389966402</v>
+        <v>2.015698116093332</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09569443719435727</v>
+        <v>0.1035859021208277</v>
       </c>
       <c r="C69">
-        <v>0.4561807843271244</v>
+        <v>0.2285163963557972</v>
       </c>
       <c r="D69">
-        <v>1.954970784327124</v>
+        <v>1.749676396355797</v>
       </c>
       <c r="E69">
-        <v>-0.001209999999999933</v>
+        <v>0.02116000000000007</v>
       </c>
       <c r="F69">
-        <v>1.49879</v>
+        <v>1.52116</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -7073,45 +7073,45 @@
         <v>0.229</v>
       </c>
       <c r="M69">
-        <v>0.113608282</v>
+        <v>0.1369044</v>
       </c>
       <c r="N69">
-        <v>0.115391718</v>
+        <v>0.09209559999999997</v>
       </c>
       <c r="O69">
-        <v>0.02192442641999999</v>
+        <v>0.01749816399999999</v>
       </c>
       <c r="P69">
-        <v>0.09346729157999997</v>
+        <v>0.07459743599999998</v>
       </c>
       <c r="Q69">
-        <v>0.15246729158</v>
+        <v>0.133597436</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1653265975586584</v>
+        <v>0.1687934441275865</v>
       </c>
       <c r="T69">
-        <v>2.189171610294069</v>
+        <v>2.252668122710213</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.19</v>
       </c>
       <c r="W69">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.015698116093332</v>
+        <v>1.672700073920195</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1035859021208277</v>
+        <v>0.1037710270472981</v>
       </c>
       <c r="C70">
-        <v>0.2285163963557972</v>
+        <v>0.2018467448224466</v>
       </c>
       <c r="D70">
-        <v>1.749676396355797</v>
+        <v>1.745376744822447</v>
       </c>
       <c r="E70">
-        <v>0.02116000000000007</v>
+        <v>0.04353000000000029</v>
       </c>
       <c r="F70">
-        <v>1.52116</v>
+        <v>1.54353</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7155,28 +7155,28 @@
         <v>0.229</v>
       </c>
       <c r="M70">
-        <v>0.1369044</v>
+        <v>0.1389177</v>
       </c>
       <c r="N70">
-        <v>0.09209559999999997</v>
+        <v>0.09008229999999995</v>
       </c>
       <c r="O70">
-        <v>0.01749816399999999</v>
+        <v>0.01711563699999999</v>
       </c>
       <c r="P70">
-        <v>0.07459743599999998</v>
+        <v>0.07296666299999996</v>
       </c>
       <c r="Q70">
-        <v>0.133597436</v>
+        <v>0.131966663</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1687934441275865</v>
+        <v>0.1724839582170906</v>
       </c>
       <c r="T70">
-        <v>2.252668122710213</v>
+        <v>2.320261184314496</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.672700073920195</v>
+        <v>1.64845804386338</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1037710270472981</v>
+        <v>0.1039561519737685</v>
       </c>
       <c r="C71">
-        <v>0.2018467448224466</v>
+        <v>0.1751981733982921</v>
       </c>
       <c r="D71">
-        <v>1.745376744822447</v>
+        <v>1.741098173398292</v>
       </c>
       <c r="E71">
-        <v>0.04353000000000029</v>
+        <v>0.06590000000000029</v>
       </c>
       <c r="F71">
-        <v>1.54353</v>
+        <v>1.5659</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7237,28 +7237,28 @@
         <v>0.229</v>
       </c>
       <c r="M71">
-        <v>0.1389177</v>
+        <v>0.140931</v>
       </c>
       <c r="N71">
-        <v>0.09008229999999995</v>
+        <v>0.08806899999999995</v>
       </c>
       <c r="O71">
-        <v>0.01711563699999999</v>
+        <v>0.01673310999999999</v>
       </c>
       <c r="P71">
-        <v>0.07296666299999996</v>
+        <v>0.07133588999999996</v>
       </c>
       <c r="Q71">
-        <v>0.131966663</v>
+        <v>0.13033589</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1724839582170906</v>
+        <v>0.1764205065792283</v>
       </c>
       <c r="T71">
-        <v>2.320261184314496</v>
+        <v>2.39236045002573</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.64845804386338</v>
+        <v>1.624908643236761</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1039561519737685</v>
+        <v>0.1041412769002389</v>
       </c>
       <c r="C72">
-        <v>0.1751981733982921</v>
+        <v>0.1485705274367255</v>
       </c>
       <c r="D72">
-        <v>1.741098173398292</v>
+        <v>1.736840527436726</v>
       </c>
       <c r="E72">
-        <v>0.06590000000000029</v>
+        <v>0.08827000000000029</v>
       </c>
       <c r="F72">
-        <v>1.5659</v>
+        <v>1.58827</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7319,28 +7319,28 @@
         <v>0.229</v>
       </c>
       <c r="M72">
-        <v>0.140931</v>
+        <v>0.1429443</v>
       </c>
       <c r="N72">
-        <v>0.08806899999999995</v>
+        <v>0.08605569999999996</v>
       </c>
       <c r="O72">
-        <v>0.01673310999999999</v>
+        <v>0.01635058299999999</v>
       </c>
       <c r="P72">
-        <v>0.07133588999999996</v>
+        <v>0.06970511699999997</v>
       </c>
       <c r="Q72">
-        <v>0.13033589</v>
+        <v>0.128705117</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1764205065792283</v>
+        <v>0.1806285410353066</v>
       </c>
       <c r="T72">
-        <v>2.39236045002573</v>
+        <v>2.469432078889463</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.624908643236761</v>
+        <v>1.602022606008074</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1041412769002389</v>
+        <v>0.1043264018267093</v>
       </c>
       <c r="C73">
-        <v>0.1485705274367259</v>
+        <v>0.1219636538001301</v>
       </c>
       <c r="D73">
-        <v>1.736840527436726</v>
+        <v>1.73260365380013</v>
       </c>
       <c r="E73">
-        <v>0.08827000000000007</v>
+        <v>0.1106400000000001</v>
       </c>
       <c r="F73">
-        <v>1.58827</v>
+        <v>1.61064</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7401,28 +7401,28 @@
         <v>0.229</v>
       </c>
       <c r="M73">
-        <v>0.1429443</v>
+        <v>0.1449576</v>
       </c>
       <c r="N73">
-        <v>0.08605569999999998</v>
+        <v>0.08404239999999999</v>
       </c>
       <c r="O73">
-        <v>0.016350583</v>
+        <v>0.015968056</v>
       </c>
       <c r="P73">
-        <v>0.06970511699999998</v>
+        <v>0.06807434399999999</v>
       </c>
       <c r="Q73">
-        <v>0.128705117</v>
+        <v>0.127074344</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1806285410353065</v>
+        <v>0.1851371493811046</v>
       </c>
       <c r="T73">
-        <v>2.469432078889462</v>
+        <v>2.552008824100605</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.602022606008074</v>
+        <v>1.57977229203574</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1043264018267093</v>
+        <v>0.1045115267531797</v>
       </c>
       <c r="C74">
-        <v>0.1219636538001301</v>
+        <v>0.09537740084151336</v>
       </c>
       <c r="D74">
-        <v>1.73260365380013</v>
+        <v>1.728387400841513</v>
       </c>
       <c r="E74">
-        <v>0.1106400000000001</v>
+        <v>0.1330100000000001</v>
       </c>
       <c r="F74">
-        <v>1.61064</v>
+        <v>1.63301</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7483,28 +7483,28 @@
         <v>0.229</v>
       </c>
       <c r="M74">
-        <v>0.1449576</v>
+        <v>0.1469709</v>
       </c>
       <c r="N74">
-        <v>0.08404239999999999</v>
+        <v>0.08202909999999999</v>
       </c>
       <c r="O74">
-        <v>0.015968056</v>
+        <v>0.015585529</v>
       </c>
       <c r="P74">
-        <v>0.06807434399999999</v>
+        <v>0.06644357099999999</v>
       </c>
       <c r="Q74">
-        <v>0.127074344</v>
+        <v>0.125443571</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1851371493811046</v>
+        <v>0.1899797287154804</v>
       </c>
       <c r="T74">
-        <v>2.552008824100605</v>
+        <v>2.640702365253313</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.57977229203574</v>
+        <v>1.558131575706483</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1045115267531797</v>
+        <v>0.1046966516796501</v>
       </c>
       <c r="C75">
-        <v>0.09537740084151336</v>
+        <v>0.06881161838642136</v>
       </c>
       <c r="D75">
-        <v>1.728387400841513</v>
+        <v>1.724191618386421</v>
       </c>
       <c r="E75">
-        <v>0.1330100000000001</v>
+        <v>0.1553800000000001</v>
       </c>
       <c r="F75">
-        <v>1.63301</v>
+        <v>1.65538</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7565,28 +7565,28 @@
         <v>0.229</v>
       </c>
       <c r="M75">
-        <v>0.1469709</v>
+        <v>0.1489842</v>
       </c>
       <c r="N75">
-        <v>0.08202909999999999</v>
+        <v>0.08001579999999997</v>
       </c>
       <c r="O75">
-        <v>0.015585529</v>
+        <v>0.01520300199999999</v>
       </c>
       <c r="P75">
-        <v>0.06644357099999999</v>
+        <v>0.06481279799999998</v>
       </c>
       <c r="Q75">
-        <v>0.125443571</v>
+        <v>0.123812798</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1899797287154804</v>
+        <v>0.1951948141525004</v>
       </c>
       <c r="T75">
-        <v>2.640702365253313</v>
+        <v>2.736218486494692</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.558131575706483</v>
+        <v>1.537075743602341</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1046966516796501</v>
+        <v>0.1048817766061205</v>
       </c>
       <c r="C76">
-        <v>0.06881161838642136</v>
+        <v>0.04226615771510267</v>
       </c>
       <c r="D76">
-        <v>1.724191618386421</v>
+        <v>1.720016157715103</v>
       </c>
       <c r="E76">
-        <v>0.1553800000000001</v>
+        <v>0.1777500000000001</v>
       </c>
       <c r="F76">
-        <v>1.65538</v>
+        <v>1.67775</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7647,28 +7647,28 @@
         <v>0.229</v>
       </c>
       <c r="M76">
-        <v>0.1489842</v>
+        <v>0.1509975</v>
       </c>
       <c r="N76">
-        <v>0.08001579999999997</v>
+        <v>0.07800249999999997</v>
       </c>
       <c r="O76">
-        <v>0.01520300199999999</v>
+        <v>0.014820475</v>
       </c>
       <c r="P76">
-        <v>0.06481279799999998</v>
+        <v>0.06318202499999998</v>
       </c>
       <c r="Q76">
-        <v>0.123812798</v>
+        <v>0.122182025</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1951948141525004</v>
+        <v>0.200827106424482</v>
       </c>
       <c r="T76">
-        <v>2.736218486494692</v>
+        <v>2.839375897435381</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.537075743602341</v>
+        <v>1.51658140035431</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1048817766061205</v>
+        <v>0.1423188539306011</v>
       </c>
       <c r="C77">
-        <v>0.04226615771510267</v>
+        <v>-0.5455368177535305</v>
       </c>
       <c r="D77">
-        <v>1.720016157715103</v>
+        <v>1.15458318224647</v>
       </c>
       <c r="E77">
-        <v>0.1777500000000001</v>
+        <v>0.2001200000000001</v>
       </c>
       <c r="F77">
-        <v>1.67775</v>
+        <v>1.70012</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7729,45 +7729,45 @@
         <v>0.229</v>
       </c>
       <c r="M77">
-        <v>0.1509975</v>
+        <v>0.249577616</v>
       </c>
       <c r="N77">
-        <v>0.07800249999999997</v>
+        <v>-0.02057761600000005</v>
       </c>
       <c r="O77">
-        <v>0.014820475</v>
+        <v>-0.003909747040000009</v>
       </c>
       <c r="P77">
-        <v>0.06318202499999998</v>
+        <v>-0.01666786896000004</v>
       </c>
       <c r="Q77">
-        <v>0.122182025</v>
+        <v>0.04233213103999996</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.200827106424482</v>
+        <v>0.2091708766256044</v>
       </c>
       <c r="T77">
-        <v>2.839375897435381</v>
+        <v>2.99219497888</v>
       </c>
       <c r="U77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.19</v>
+        <v>0.1743345444889577</v>
       </c>
       <c r="W77">
-        <v>0.07290000000000001</v>
+        <v>0.121207688869021</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.51658140035431</v>
+        <v>0.9175502341524088</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1423188539306011</v>
+        <v>0.143328853930601</v>
       </c>
       <c r="C78">
-        <v>-0.5455368177535305</v>
+        <v>-0.5780566426769018</v>
       </c>
       <c r="D78">
-        <v>1.15458318224647</v>
+        <v>1.144433357323098</v>
       </c>
       <c r="E78">
-        <v>0.2001200000000001</v>
+        <v>0.2224900000000001</v>
       </c>
       <c r="F78">
-        <v>1.70012</v>
+        <v>1.72249</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7811,37 +7811,37 @@
         <v>0.229</v>
       </c>
       <c r="M78">
-        <v>0.249577616</v>
+        <v>0.2528615320000001</v>
       </c>
       <c r="N78">
-        <v>-0.02057761600000005</v>
+        <v>-0.02386153200000007</v>
       </c>
       <c r="O78">
-        <v>-0.003909747040000009</v>
+        <v>-0.004533691080000014</v>
       </c>
       <c r="P78">
-        <v>-0.01666786896000004</v>
+        <v>-0.01932784092000006</v>
       </c>
       <c r="Q78">
-        <v>0.04233213103999996</v>
+        <v>0.03967215907999994</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2091708766256044</v>
+        <v>0.216273958218022</v>
       </c>
       <c r="T78">
-        <v>2.99219497888</v>
+        <v>3.122290412744348</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1743345444889577</v>
+        <v>0.1720704594955946</v>
       </c>
       <c r="W78">
-        <v>0.121207688869021</v>
+        <v>0.1215400565460467</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9175502341524088</v>
+        <v>0.9056339973452345</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.143328853930601</v>
+        <v>0.144338853930601</v>
       </c>
       <c r="C79">
-        <v>-0.5780566426769018</v>
+        <v>-0.6103995704996665</v>
       </c>
       <c r="D79">
-        <v>1.144433357323098</v>
+        <v>1.134460429500334</v>
       </c>
       <c r="E79">
-        <v>0.2224900000000001</v>
+        <v>0.2448600000000001</v>
       </c>
       <c r="F79">
-        <v>1.72249</v>
+        <v>1.74486</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7893,37 +7893,37 @@
         <v>0.229</v>
       </c>
       <c r="M79">
-        <v>0.2528615320000001</v>
+        <v>0.2561454480000001</v>
       </c>
       <c r="N79">
-        <v>-0.02386153200000007</v>
+        <v>-0.02714544800000007</v>
       </c>
       <c r="O79">
-        <v>-0.004533691080000014</v>
+        <v>-0.005157635120000014</v>
       </c>
       <c r="P79">
-        <v>-0.01932784092000006</v>
+        <v>-0.02198781288000006</v>
       </c>
       <c r="Q79">
-        <v>0.03967215907999994</v>
+        <v>0.03701218711999994</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.216273958218022</v>
+        <v>0.2240227745006594</v>
       </c>
       <c r="T79">
-        <v>3.122290412744348</v>
+        <v>3.264212704232728</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1720704594955946</v>
+        <v>0.1698644279635998</v>
       </c>
       <c r="W79">
-        <v>0.1215400565460467</v>
+        <v>0.1218639019749436</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9056339973452345</v>
+        <v>0.8940233050715777</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.144338853930601</v>
+        <v>0.145348853930601</v>
       </c>
       <c r="C80">
-        <v>-0.6103995704996665</v>
+        <v>-0.6425701858694624</v>
       </c>
       <c r="D80">
-        <v>1.134460429500334</v>
+        <v>1.124659814130538</v>
       </c>
       <c r="E80">
-        <v>0.2448600000000001</v>
+        <v>0.2672300000000001</v>
       </c>
       <c r="F80">
-        <v>1.74486</v>
+        <v>1.76723</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7975,37 +7975,37 @@
         <v>0.229</v>
       </c>
       <c r="M80">
-        <v>0.2561454480000001</v>
+        <v>0.2594293640000001</v>
       </c>
       <c r="N80">
-        <v>-0.02714544800000007</v>
+        <v>-0.03042936400000007</v>
       </c>
       <c r="O80">
-        <v>-0.005157635120000014</v>
+        <v>-0.005781579160000013</v>
       </c>
       <c r="P80">
-        <v>-0.02198781288000006</v>
+        <v>-0.02464778484000005</v>
       </c>
       <c r="Q80">
-        <v>0.03701218711999994</v>
+        <v>0.03435221515999994</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2240227745006594</v>
+        <v>0.2325095732864051</v>
       </c>
       <c r="T80">
-        <v>3.264212704232728</v>
+        <v>3.419651404434287</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1698644279635998</v>
+        <v>0.1677142453311491</v>
       </c>
       <c r="W80">
-        <v>0.1218639019749436</v>
+        <v>0.1221795487853873</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8940233050715777</v>
+        <v>0.8827065543744691</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.145348853930601</v>
+        <v>0.1463588539306011</v>
       </c>
       <c r="C81">
-        <v>-0.6425701858694624</v>
+        <v>-0.6745729163635865</v>
       </c>
       <c r="D81">
-        <v>1.124659814130538</v>
+        <v>1.115027083636414</v>
       </c>
       <c r="E81">
-        <v>0.2672300000000001</v>
+        <v>0.2896000000000001</v>
       </c>
       <c r="F81">
-        <v>1.76723</v>
+        <v>1.7896</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -8057,37 +8057,37 @@
         <v>0.229</v>
       </c>
       <c r="M81">
-        <v>0.2594293640000001</v>
+        <v>0.26271328</v>
       </c>
       <c r="N81">
-        <v>-0.03042936400000007</v>
+        <v>-0.03371328000000007</v>
       </c>
       <c r="O81">
-        <v>-0.005781579160000013</v>
+        <v>-0.006405523200000013</v>
       </c>
       <c r="P81">
-        <v>-0.02464778484000005</v>
+        <v>-0.02730775680000005</v>
       </c>
       <c r="Q81">
-        <v>0.03435221515999994</v>
+        <v>0.03169224319999994</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2325095732864051</v>
+        <v>0.2418450519507253</v>
       </c>
       <c r="T81">
-        <v>3.419651404434287</v>
+        <v>3.590633974656001</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1677142453311491</v>
+        <v>0.1656178172645098</v>
       </c>
       <c r="W81">
-        <v>0.1221795487853873</v>
+        <v>0.12248730442557</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8827065543744691</v>
+        <v>0.8716727224447882</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1463588539306011</v>
+        <v>0.147368853930601</v>
       </c>
       <c r="C82">
-        <v>-0.6745729163635865</v>
+        <v>-0.7064120391584237</v>
       </c>
       <c r="D82">
-        <v>1.115027083636414</v>
+        <v>1.105557960841577</v>
       </c>
       <c r="E82">
-        <v>0.2896000000000001</v>
+        <v>0.3119700000000003</v>
       </c>
       <c r="F82">
-        <v>1.7896</v>
+        <v>1.81197</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8139,37 +8139,37 @@
         <v>0.229</v>
       </c>
       <c r="M82">
-        <v>0.26271328</v>
+        <v>0.265997196</v>
       </c>
       <c r="N82">
-        <v>-0.03371328000000007</v>
+        <v>-0.03699719600000007</v>
       </c>
       <c r="O82">
-        <v>-0.006405523200000013</v>
+        <v>-0.007029467240000012</v>
       </c>
       <c r="P82">
-        <v>-0.02730775680000005</v>
+        <v>-0.02996772876000005</v>
       </c>
       <c r="Q82">
-        <v>0.03169224319999994</v>
+        <v>0.02903227123999994</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2418450519507253</v>
+        <v>0.2521632125797109</v>
       </c>
       <c r="T82">
-        <v>3.590633974656001</v>
+        <v>3.779614710164211</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1656178172645098</v>
+        <v>0.1635731528538368</v>
       </c>
       <c r="W82">
-        <v>0.12248730442557</v>
+        <v>0.1227874611610568</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8716727224447882</v>
+        <v>0.8609113308096674</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.147368853930601</v>
+        <v>0.148378853930601</v>
       </c>
       <c r="C83">
-        <v>-0.7064120391584237</v>
+        <v>-0.7380916873618999</v>
       </c>
       <c r="D83">
-        <v>1.105557960841577</v>
+        <v>1.0962483126381</v>
       </c>
       <c r="E83">
-        <v>0.3119700000000003</v>
+        <v>0.3343400000000003</v>
       </c>
       <c r="F83">
-        <v>1.81197</v>
+        <v>1.83434</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8221,37 +8221,37 @@
         <v>0.229</v>
       </c>
       <c r="M83">
-        <v>0.265997196</v>
+        <v>0.269281112</v>
       </c>
       <c r="N83">
-        <v>-0.03699719600000007</v>
+        <v>-0.04028111200000006</v>
       </c>
       <c r="O83">
-        <v>-0.007029467240000012</v>
+        <v>-0.007653411280000012</v>
       </c>
       <c r="P83">
-        <v>-0.02996772876000005</v>
+        <v>-0.03262770072000005</v>
       </c>
       <c r="Q83">
-        <v>0.02903227123999994</v>
+        <v>0.02637229927999995</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2521632125797109</v>
+        <v>0.2636278355008059</v>
       </c>
       <c r="T83">
-        <v>3.779614710164211</v>
+        <v>3.989593305173334</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1635731528538368</v>
+        <v>0.1615783583068388</v>
       </c>
       <c r="W83">
-        <v>0.1227874611610568</v>
+        <v>0.1230802970005561</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8609113308096674</v>
+        <v>0.8504124121412568</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.148378853930601</v>
+        <v>0.149388853930601</v>
       </c>
       <c r="C84">
-        <v>-0.7380916873618999</v>
+        <v>-0.7696158560286683</v>
       </c>
       <c r="D84">
-        <v>1.0962483126381</v>
+        <v>1.087094143971332</v>
       </c>
       <c r="E84">
-        <v>0.3343400000000003</v>
+        <v>0.3567100000000003</v>
       </c>
       <c r="F84">
-        <v>1.83434</v>
+        <v>1.85671</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8303,37 +8303,37 @@
         <v>0.229</v>
       </c>
       <c r="M84">
-        <v>0.269281112</v>
+        <v>0.2725650280000001</v>
       </c>
       <c r="N84">
-        <v>-0.04028111200000006</v>
+        <v>-0.04356502800000012</v>
       </c>
       <c r="O84">
-        <v>-0.007653411280000012</v>
+        <v>-0.008277355320000021</v>
       </c>
       <c r="P84">
-        <v>-0.03262770072000005</v>
+        <v>-0.0352876726800001</v>
       </c>
       <c r="Q84">
-        <v>0.02637229927999995</v>
+        <v>0.0237123273199999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2636278355008059</v>
+        <v>0.2764412375890886</v>
       </c>
       <c r="T84">
-        <v>3.989593305173334</v>
+        <v>4.224275264301178</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1615783583068388</v>
+        <v>0.1596316310983227</v>
       </c>
       <c r="W84">
-        <v>0.1230802970005561</v>
+        <v>0.1233660765547662</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8504124121412568</v>
+        <v>0.840166479464856</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.149388853930601</v>
+        <v>0.150398853930601</v>
       </c>
       <c r="C85">
-        <v>-0.7696158560286683</v>
+        <v>-0.8009884078764102</v>
       </c>
       <c r="D85">
-        <v>1.087094143971332</v>
+        <v>1.07809159212359</v>
       </c>
       <c r="E85">
-        <v>0.3567100000000003</v>
+        <v>0.3790800000000003</v>
       </c>
       <c r="F85">
-        <v>1.85671</v>
+        <v>1.87908</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8385,37 +8385,37 @@
         <v>0.229</v>
       </c>
       <c r="M85">
-        <v>0.2725650280000001</v>
+        <v>0.2758489440000001</v>
       </c>
       <c r="N85">
-        <v>-0.04356502800000012</v>
+        <v>-0.04684894400000011</v>
       </c>
       <c r="O85">
-        <v>-0.008277355320000021</v>
+        <v>-0.008901299360000023</v>
       </c>
       <c r="P85">
-        <v>-0.0352876726800001</v>
+        <v>-0.03794764464000009</v>
       </c>
       <c r="Q85">
-        <v>0.0237123273199999</v>
+        <v>0.02105235535999991</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2764412375890886</v>
+        <v>0.2908563149384067</v>
       </c>
       <c r="T85">
-        <v>4.224275264301178</v>
+        <v>4.488292468320003</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1596316310983227</v>
+        <v>0.1577312545376283</v>
       </c>
       <c r="W85">
-        <v>0.1233660765547662</v>
+        <v>0.1236450518338762</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.840166479464856</v>
+        <v>0.8301644975664648</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.150398853930601</v>
+        <v>0.1514088539306011</v>
       </c>
       <c r="C86">
-        <v>-0.80098840787641</v>
+        <v>-0.8322130787204405</v>
       </c>
       <c r="D86">
-        <v>1.07809159212359</v>
+        <v>1.06923692127956</v>
       </c>
       <c r="E86">
-        <v>0.3790800000000001</v>
+        <v>0.4014500000000001</v>
       </c>
       <c r="F86">
-        <v>1.87908</v>
+        <v>1.90145</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8467,37 +8467,37 @@
         <v>0.229</v>
       </c>
       <c r="M86">
-        <v>0.275848944</v>
+        <v>0.27913286</v>
       </c>
       <c r="N86">
-        <v>-0.04684894400000006</v>
+        <v>-0.05013286000000006</v>
       </c>
       <c r="O86">
-        <v>-0.008901299360000012</v>
+        <v>-0.009525243400000011</v>
       </c>
       <c r="P86">
-        <v>-0.03794764464000005</v>
+        <v>-0.04060761660000005</v>
       </c>
       <c r="Q86">
-        <v>0.02105235535999995</v>
+        <v>0.01839238339999995</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2908563149384066</v>
+        <v>0.3071934026009671</v>
       </c>
       <c r="T86">
-        <v>4.488292468319999</v>
+        <v>4.787511966208</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1577312545376284</v>
+        <v>0.1558755927195386</v>
       </c>
       <c r="W86">
-        <v>0.1236450518338762</v>
+        <v>0.1239174629887718</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.830164497566465</v>
+        <v>0.8203978564186243</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1514088539306011</v>
+        <v>0.152418853930601</v>
       </c>
       <c r="C87">
-        <v>-0.8322130787204405</v>
+        <v>-0.8632934826426784</v>
       </c>
       <c r="D87">
-        <v>1.06923692127956</v>
+        <v>1.060526517357322</v>
       </c>
       <c r="E87">
-        <v>0.4014500000000001</v>
+        <v>0.4238200000000001</v>
       </c>
       <c r="F87">
-        <v>1.90145</v>
+        <v>1.92382</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8549,37 +8549,37 @@
         <v>0.229</v>
       </c>
       <c r="M87">
-        <v>0.27913286</v>
+        <v>0.282416776</v>
       </c>
       <c r="N87">
-        <v>-0.05013286000000006</v>
+        <v>-0.05341677600000005</v>
       </c>
       <c r="O87">
-        <v>-0.009525243400000011</v>
+        <v>-0.01014918744000001</v>
       </c>
       <c r="P87">
-        <v>-0.04060761660000005</v>
+        <v>-0.04326758856000004</v>
       </c>
       <c r="Q87">
-        <v>0.01839238339999995</v>
+        <v>0.01573241143999995</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3071934026009671</v>
+        <v>0.3258643599296075</v>
       </c>
       <c r="T87">
-        <v>4.787511966208</v>
+        <v>5.129477106651428</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1558755927195386</v>
+        <v>0.154063085827451</v>
       </c>
       <c r="W87">
-        <v>0.1239174629887718</v>
+        <v>0.1241835390005302</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8203978564186243</v>
+        <v>0.8108583464602682</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.152418853930601</v>
+        <v>0.153428853930601</v>
       </c>
       <c r="C88">
-        <v>-0.8632934826426784</v>
+        <v>-0.8942331169100088</v>
       </c>
       <c r="D88">
-        <v>1.060526517357322</v>
+        <v>1.051956883089991</v>
       </c>
       <c r="E88">
-        <v>0.4238200000000001</v>
+        <v>0.4461900000000001</v>
       </c>
       <c r="F88">
-        <v>1.92382</v>
+        <v>1.94619</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8631,37 +8631,37 @@
         <v>0.229</v>
       </c>
       <c r="M88">
-        <v>0.282416776</v>
+        <v>0.285700692</v>
       </c>
       <c r="N88">
-        <v>-0.05341677600000005</v>
+        <v>-0.05670069200000005</v>
       </c>
       <c r="O88">
-        <v>-0.01014918744000001</v>
+        <v>-0.01077313148000001</v>
       </c>
       <c r="P88">
-        <v>-0.04326758856000004</v>
+        <v>-0.04592756052000004</v>
       </c>
       <c r="Q88">
-        <v>0.01573241143999995</v>
+        <v>0.01307243947999995</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3258643599296075</v>
+        <v>0.3474077722318851</v>
       </c>
       <c r="T88">
-        <v>5.129477106651428</v>
+        <v>5.524052268701539</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.154063085827451</v>
+        <v>0.1522922457604688</v>
       </c>
       <c r="W88">
-        <v>0.1241835390005302</v>
+        <v>0.1244434983223632</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8108583464602682</v>
+        <v>0.8015381355814145</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.153428853930601</v>
+        <v>0.2035692793462262</v>
       </c>
       <c r="C89">
-        <v>-0.8942331169100088</v>
+        <v>-1.217779236154665</v>
       </c>
       <c r="D89">
-        <v>1.051956883089991</v>
+        <v>0.7507807638453349</v>
       </c>
       <c r="E89">
-        <v>0.4461900000000001</v>
+        <v>0.4685600000000001</v>
       </c>
       <c r="F89">
-        <v>1.94619</v>
+        <v>1.96856</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8713,45 +8713,45 @@
         <v>0.229</v>
       </c>
       <c r="M89">
-        <v>0.285700692</v>
+        <v>0.395286848</v>
       </c>
       <c r="N89">
-        <v>-0.05670069200000005</v>
+        <v>-0.166286848</v>
       </c>
       <c r="O89">
-        <v>-0.01077313148000001</v>
+        <v>-0.03159450112000001</v>
       </c>
       <c r="P89">
-        <v>-0.04592756052000004</v>
+        <v>-0.13469234688</v>
       </c>
       <c r="Q89">
-        <v>0.01307243947999995</v>
+        <v>-0.07569234688000004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3474077722318851</v>
+        <v>0.3859619650480855</v>
       </c>
       <c r="T89">
-        <v>5.524052268701539</v>
+        <v>6.230185849803509</v>
       </c>
       <c r="U89">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1522922457604688</v>
+        <v>0.1100719647520375</v>
       </c>
       <c r="W89">
-        <v>0.1244434983223632</v>
+        <v>0.1786975494777909</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8015381355814145</v>
+        <v>0.5793261302738815</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2035692793462262</v>
+        <v>0.2051192793462262</v>
       </c>
       <c r="C90">
-        <v>-1.217779236154665</v>
+        <v>-1.246735704573162</v>
       </c>
       <c r="D90">
-        <v>0.7507807638453349</v>
+        <v>0.7441942954268378</v>
       </c>
       <c r="E90">
-        <v>0.4685600000000001</v>
+        <v>0.4909300000000001</v>
       </c>
       <c r="F90">
-        <v>1.96856</v>
+        <v>1.99093</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8795,37 +8795,37 @@
         <v>0.229</v>
       </c>
       <c r="M90">
-        <v>0.395286848</v>
+        <v>0.399778744</v>
       </c>
       <c r="N90">
-        <v>-0.166286848</v>
+        <v>-0.170778744</v>
       </c>
       <c r="O90">
-        <v>-0.03159450112000001</v>
+        <v>-0.03244796136000001</v>
       </c>
       <c r="P90">
-        <v>-0.13469234688</v>
+        <v>-0.13833078264</v>
       </c>
       <c r="Q90">
-        <v>-0.07569234688000004</v>
+        <v>-0.07933078264000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3859619650480855</v>
+        <v>0.4168857800524569</v>
       </c>
       <c r="T90">
-        <v>6.230185849803509</v>
+        <v>6.796566381603827</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1100719647520375</v>
+        <v>0.1088352011031382</v>
       </c>
       <c r="W90">
-        <v>0.1786975494777909</v>
+        <v>0.1789458916184899</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5793261302738815</v>
+        <v>0.5728168479112535</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2051192793462262</v>
+        <v>0.2066692793462262</v>
       </c>
       <c r="C91">
-        <v>-1.246735704573162</v>
+        <v>-1.275577614124098</v>
       </c>
       <c r="D91">
-        <v>0.7441942954268378</v>
+        <v>0.7377223858759018</v>
       </c>
       <c r="E91">
-        <v>0.4909300000000001</v>
+        <v>0.5133000000000001</v>
       </c>
       <c r="F91">
-        <v>1.99093</v>
+        <v>2.0133</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8877,37 +8877,37 @@
         <v>0.229</v>
       </c>
       <c r="M91">
-        <v>0.399778744</v>
+        <v>0.40427064</v>
       </c>
       <c r="N91">
-        <v>-0.170778744</v>
+        <v>-0.17527064</v>
       </c>
       <c r="O91">
-        <v>-0.03244796136000001</v>
+        <v>-0.03330142160000001</v>
       </c>
       <c r="P91">
-        <v>-0.13833078264</v>
+        <v>-0.1419692184</v>
       </c>
       <c r="Q91">
-        <v>-0.07933078264000004</v>
+        <v>-0.08296921840000004</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4168857800524569</v>
+        <v>0.4539943580577026</v>
       </c>
       <c r="T91">
-        <v>6.796566381603827</v>
+        <v>7.476223019764212</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1088352011031382</v>
+        <v>0.1076259210908811</v>
       </c>
       <c r="W91">
-        <v>0.1789458916184899</v>
+        <v>0.1791887150449511</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5728168479112535</v>
+        <v>0.5664522162677952</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2066692793462262</v>
+        <v>0.2082192793462262</v>
       </c>
       <c r="C92">
-        <v>-1.275577614124098</v>
+        <v>-1.304307927834013</v>
       </c>
       <c r="D92">
-        <v>0.7377223858759018</v>
+        <v>0.731362072165987</v>
       </c>
       <c r="E92">
-        <v>0.5133000000000001</v>
+        <v>0.5356700000000001</v>
       </c>
       <c r="F92">
-        <v>2.0133</v>
+        <v>2.03567</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8959,37 +8959,37 @@
         <v>0.229</v>
       </c>
       <c r="M92">
-        <v>0.40427064</v>
+        <v>0.408762536</v>
       </c>
       <c r="N92">
-        <v>-0.17527064</v>
+        <v>-0.179762536</v>
       </c>
       <c r="O92">
-        <v>-0.03330142160000001</v>
+        <v>-0.03415488184000001</v>
       </c>
       <c r="P92">
-        <v>-0.1419692184</v>
+        <v>-0.14560765416</v>
       </c>
       <c r="Q92">
-        <v>-0.08296921840000004</v>
+        <v>-0.08660765416000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4539943580577026</v>
+        <v>0.4993492867307807</v>
       </c>
       <c r="T92">
-        <v>7.476223019764212</v>
+        <v>8.306914466404679</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1076259210908811</v>
+        <v>0.106443218661311</v>
       </c>
       <c r="W92">
-        <v>0.1791887150449511</v>
+        <v>0.1794262016928088</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5664522162677952</v>
+        <v>0.5602274666384788</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2082192793462262</v>
+        <v>0.2097692793462262</v>
       </c>
       <c r="C93">
-        <v>-1.304307927834013</v>
+        <v>-1.332929507419317</v>
       </c>
       <c r="D93">
-        <v>0.731362072165987</v>
+        <v>0.7251104925806827</v>
       </c>
       <c r="E93">
-        <v>0.5356700000000001</v>
+        <v>0.5580400000000001</v>
       </c>
       <c r="F93">
-        <v>2.03567</v>
+        <v>2.05804</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -9041,37 +9041,37 @@
         <v>0.229</v>
       </c>
       <c r="M93">
-        <v>0.408762536</v>
+        <v>0.413254432</v>
       </c>
       <c r="N93">
-        <v>-0.179762536</v>
+        <v>-0.184254432</v>
       </c>
       <c r="O93">
-        <v>-0.03415488184000001</v>
+        <v>-0.03500834208</v>
       </c>
       <c r="P93">
-        <v>-0.14560765416</v>
+        <v>-0.14924608992</v>
       </c>
       <c r="Q93">
-        <v>-0.08660765416000002</v>
+        <v>-0.09024608992000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4993492867307807</v>
+        <v>0.5560429475721284</v>
       </c>
       <c r="T93">
-        <v>8.306914466404679</v>
+        <v>9.345278774705267</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.106443218661311</v>
+        <v>0.1052862271541228</v>
       </c>
       <c r="W93">
-        <v>0.1794262016928088</v>
+        <v>0.1796585255874521</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5602274666384788</v>
+        <v>0.5541380376532778</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2097692793462262</v>
+        <v>0.2113192793462262</v>
       </c>
       <c r="C94">
-        <v>-1.332929507419317</v>
+        <v>-1.361445117579521</v>
       </c>
       <c r="D94">
-        <v>0.7251104925806827</v>
+        <v>0.7189648824204795</v>
       </c>
       <c r="E94">
-        <v>0.5580400000000001</v>
+        <v>0.5804100000000001</v>
       </c>
       <c r="F94">
-        <v>2.05804</v>
+        <v>2.08041</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -9123,37 +9123,37 @@
         <v>0.229</v>
       </c>
       <c r="M94">
-        <v>0.413254432</v>
+        <v>0.4177463280000001</v>
       </c>
       <c r="N94">
-        <v>-0.184254432</v>
+        <v>-0.1887463280000001</v>
       </c>
       <c r="O94">
-        <v>-0.03500834208</v>
+        <v>-0.03586180232000002</v>
       </c>
       <c r="P94">
-        <v>-0.14924608992</v>
+        <v>-0.15288452568</v>
       </c>
       <c r="Q94">
-        <v>-0.09024608992000002</v>
+        <v>-0.09388452568000005</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5560429475721284</v>
+        <v>0.6289347972252897</v>
       </c>
       <c r="T94">
-        <v>9.345278774705267</v>
+        <v>10.68031859966316</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1052862271541228</v>
+        <v>0.1041541171847236</v>
       </c>
       <c r="W94">
-        <v>0.1796585255874521</v>
+        <v>0.1798858532693075</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5541380376532778</v>
+        <v>0.5481795641301244</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2113192793462262</v>
+        <v>0.2128692793462262</v>
       </c>
       <c r="C95">
-        <v>-1.361445117579521</v>
+        <v>-1.389857430073969</v>
       </c>
       <c r="D95">
-        <v>0.7189648824204795</v>
+        <v>0.7129225699260314</v>
       </c>
       <c r="E95">
-        <v>0.5804100000000001</v>
+        <v>0.6027800000000001</v>
       </c>
       <c r="F95">
-        <v>2.08041</v>
+        <v>2.10278</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9205,37 +9205,37 @@
         <v>0.229</v>
       </c>
       <c r="M95">
-        <v>0.4177463280000001</v>
+        <v>0.4222382240000001</v>
       </c>
       <c r="N95">
-        <v>-0.1887463280000001</v>
+        <v>-0.1932382240000001</v>
       </c>
       <c r="O95">
-        <v>-0.03586180232000002</v>
+        <v>-0.03671526256000002</v>
       </c>
       <c r="P95">
-        <v>-0.15288452568</v>
+        <v>-0.1565229614400001</v>
       </c>
       <c r="Q95">
-        <v>-0.09388452568000005</v>
+        <v>-0.09752296144000006</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6289347972252897</v>
+        <v>0.7261239300961715</v>
       </c>
       <c r="T95">
-        <v>10.68031859966316</v>
+        <v>12.46037169960703</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1041541171847236</v>
+        <v>0.1030460946614819</v>
       </c>
       <c r="W95">
-        <v>0.1798858532693075</v>
+        <v>0.1801083441919744</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5481795641301244</v>
+        <v>0.5423478666393784</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2128692793462262</v>
+        <v>0.2144192793462263</v>
       </c>
       <c r="C96">
-        <v>-1.389857430073969</v>
+        <v>-1.418169027594727</v>
       </c>
       <c r="D96">
-        <v>0.7129225699260314</v>
+        <v>0.7069809724052735</v>
       </c>
       <c r="E96">
-        <v>0.6027800000000001</v>
+        <v>0.6251500000000001</v>
       </c>
       <c r="F96">
-        <v>2.10278</v>
+        <v>2.12515</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9287,37 +9287,37 @@
         <v>0.229</v>
       </c>
       <c r="M96">
-        <v>0.4222382240000001</v>
+        <v>0.42673012</v>
       </c>
       <c r="N96">
-        <v>-0.1932382240000001</v>
+        <v>-0.1977301200000001</v>
       </c>
       <c r="O96">
-        <v>-0.03671526256000002</v>
+        <v>-0.03756872280000001</v>
       </c>
       <c r="P96">
-        <v>-0.1565229614400001</v>
+        <v>-0.1601613972000001</v>
       </c>
       <c r="Q96">
-        <v>-0.09752296144000006</v>
+        <v>-0.1011613972000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7261239300961715</v>
+        <v>0.8621887161154063</v>
       </c>
       <c r="T96">
-        <v>12.46037169960703</v>
+        <v>14.95244603952844</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1030460946614819</v>
+        <v>0.1019613989282031</v>
       </c>
       <c r="W96">
-        <v>0.1801083441919744</v>
+        <v>0.1803261510952168</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5423478666393784</v>
+        <v>0.5366389417273849</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2144192793462263</v>
+        <v>0.2159692793462262</v>
       </c>
       <c r="C97">
-        <v>-1.418169027594727</v>
+        <v>-1.446382407447398</v>
       </c>
       <c r="D97">
-        <v>0.7069809724052735</v>
+        <v>0.7011375925526019</v>
       </c>
       <c r="E97">
-        <v>0.6251500000000001</v>
+        <v>0.6475200000000001</v>
       </c>
       <c r="F97">
-        <v>2.12515</v>
+        <v>2.14752</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9369,37 +9369,37 @@
         <v>0.229</v>
       </c>
       <c r="M97">
-        <v>0.42673012</v>
+        <v>0.431222016</v>
       </c>
       <c r="N97">
-        <v>-0.1977301200000001</v>
+        <v>-0.2022220160000001</v>
       </c>
       <c r="O97">
-        <v>-0.03756872280000001</v>
+        <v>-0.03842218304000001</v>
       </c>
       <c r="P97">
-        <v>-0.1601613972000001</v>
+        <v>-0.1637998329600001</v>
       </c>
       <c r="Q97">
-        <v>-0.1011613972000001</v>
+        <v>-0.1047998329600001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8621887161154063</v>
+        <v>1.066285895144258</v>
       </c>
       <c r="T97">
-        <v>14.95244603952844</v>
+        <v>18.69055754941056</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1019613989282031</v>
+        <v>0.100899301022701</v>
       </c>
       <c r="W97">
-        <v>0.1803261510952168</v>
+        <v>0.1805394203546416</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5366389417273849</v>
+        <v>0.531048952751058</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2159692793462262</v>
+        <v>0.2175192793462262</v>
       </c>
       <c r="C98">
-        <v>-1.446382407447398</v>
+        <v>-1.474499985050906</v>
       </c>
       <c r="D98">
-        <v>0.7011375925526019</v>
+        <v>0.6953900149490946</v>
       </c>
       <c r="E98">
-        <v>0.6475200000000001</v>
+        <v>0.6698900000000001</v>
       </c>
       <c r="F98">
-        <v>2.14752</v>
+        <v>2.16989</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9451,37 +9451,37 @@
         <v>0.229</v>
       </c>
       <c r="M98">
-        <v>0.431222016</v>
+        <v>0.435713912</v>
       </c>
       <c r="N98">
-        <v>-0.2022220160000001</v>
+        <v>-0.2067139120000001</v>
       </c>
       <c r="O98">
-        <v>-0.03842218304000001</v>
+        <v>-0.03927564328000001</v>
       </c>
       <c r="P98">
-        <v>-0.1637998329600001</v>
+        <v>-0.1674382687200001</v>
       </c>
       <c r="Q98">
-        <v>-0.1047998329600001</v>
+        <v>-0.1084382687200001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.066285895144256</v>
+        <v>1.406447860192341</v>
       </c>
       <c r="T98">
-        <v>18.69055754941051</v>
+        <v>24.92074339921401</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.100899301022701</v>
+        <v>0.09985910204308554</v>
       </c>
       <c r="W98">
-        <v>0.1805394203546416</v>
+        <v>0.1807482923097484</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.531048952751058</v>
+        <v>0.5255742212793976</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2175192793462262</v>
+        <v>0.2190692793462262</v>
       </c>
       <c r="C99">
-        <v>-1.474499985050906</v>
+        <v>-1.502524097266531</v>
       </c>
       <c r="D99">
-        <v>0.6953900149490946</v>
+        <v>0.6897359027334691</v>
       </c>
       <c r="E99">
-        <v>0.6698900000000001</v>
+        <v>0.6922600000000001</v>
       </c>
       <c r="F99">
-        <v>2.16989</v>
+        <v>2.19226</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9533,37 +9533,37 @@
         <v>0.229</v>
       </c>
       <c r="M99">
-        <v>0.435713912</v>
+        <v>0.440205808</v>
       </c>
       <c r="N99">
-        <v>-0.2067139120000001</v>
+        <v>-0.2112058080000001</v>
       </c>
       <c r="O99">
-        <v>-0.03927564328000001</v>
+        <v>-0.04012910352000001</v>
       </c>
       <c r="P99">
-        <v>-0.1674382687200001</v>
+        <v>-0.17107670448</v>
       </c>
       <c r="Q99">
-        <v>-0.1084382687200001</v>
+        <v>-0.11207670448</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.406447860192341</v>
+        <v>2.086771790288511</v>
       </c>
       <c r="T99">
-        <v>24.92074339921401</v>
+        <v>37.38111509882102</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09985910204308554</v>
+        <v>0.09884013161407446</v>
       </c>
       <c r="W99">
-        <v>0.1807482923097484</v>
+        <v>0.1809529015718939</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5255742212793976</v>
+        <v>0.5202112190214445</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2190692793462262</v>
+        <v>0.2206192793462262</v>
       </c>
       <c r="C100">
-        <v>-1.502524097266531</v>
+        <v>-1.530457005565861</v>
       </c>
       <c r="D100">
-        <v>0.6897359027334691</v>
+        <v>0.6841729944341394</v>
       </c>
       <c r="E100">
-        <v>0.6922600000000001</v>
+        <v>0.7146300000000001</v>
       </c>
       <c r="F100">
-        <v>2.19226</v>
+        <v>2.21463</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9615,37 +9615,37 @@
         <v>0.229</v>
       </c>
       <c r="M100">
-        <v>0.440205808</v>
+        <v>0.444697704</v>
       </c>
       <c r="N100">
-        <v>-0.2112058080000001</v>
+        <v>-0.215697704</v>
       </c>
       <c r="O100">
-        <v>-0.04012910352000001</v>
+        <v>-0.04098256376000001</v>
       </c>
       <c r="P100">
-        <v>-0.17107670448</v>
+        <v>-0.17471514024</v>
       </c>
       <c r="Q100">
-        <v>-0.11207670448</v>
+        <v>-0.11571514024</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.086771790288511</v>
+        <v>4.127743580577022</v>
       </c>
       <c r="T100">
-        <v>37.38111509882102</v>
+        <v>74.76223019764204</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09884013161407446</v>
+        <v>0.09784174644625553</v>
       </c>
       <c r="W100">
-        <v>0.1809529015718939</v>
+        <v>0.1811533773135919</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5202112190214445</v>
+        <v>0.5149565602434502</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2206192793462262</v>
-      </c>
-      <c r="C101">
-        <v>-1.530457005565861</v>
-      </c>
-      <c r="D101">
-        <v>0.6841729944341394</v>
-      </c>
-      <c r="E101">
-        <v>0.7146300000000001</v>
-      </c>
-      <c r="F101">
-        <v>2.21463</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>0.737</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.288</v>
-      </c>
-      <c r="K101">
-        <v>0.059</v>
-      </c>
-      <c r="L101">
-        <v>0.229</v>
-      </c>
-      <c r="M101">
-        <v>0.444697704</v>
-      </c>
-      <c r="N101">
-        <v>-0.215697704</v>
-      </c>
-      <c r="O101">
-        <v>-0.04098256376000001</v>
-      </c>
-      <c r="P101">
-        <v>-0.17471514024</v>
-      </c>
-      <c r="Q101">
-        <v>-0.11571514024</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.127743580577022</v>
-      </c>
-      <c r="T101">
-        <v>74.76223019764204</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09784174644625553</v>
-      </c>
-      <c r="W101">
-        <v>0.1811533773135919</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5149565602434502</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
